--- a/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-06-24.xlsx
+++ b/docs/trackers/exports/IH35-TMS-BLOCK-RECONCILIATION-2026-06-24.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="847">
-  <si>
-    <t>IH35-TMS — EVERY BLOCK, BUILT vs PENDING — 2026-06-24 (verified vs origin/main + 1369 merged PRs)</t>
-  </si>
-  <si>
-    <t>DONE = on main now · PENDING = needs build · PENDING (GATED) = financial/locked, needs Jorge's gate first</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2755" uniqueCount="860">
+  <si>
+    <t>IH35-TMS — EVERY BLOCK, BUILT vs PENDING — 2026-06-24 (verified vs origin/main + 1370 merged PRs)</t>
+  </si>
+  <si>
+    <t>DONE = verified on main (branch merged or files present) · NEEDS-VERIFY = weak signal, not trusted until GUARD confirms · PENDING = needs build · PENDING (GATED) = financial/locked, needs Jorge's gate first</t>
   </si>
   <si>
     <t>Block</t>
@@ -416,6 +416,519 @@
     <t>GATED (launch July 2026). Tier 1 (new entity going live). STOPS for Jorge.</t>
   </si>
   <si>
+    <t>AF-0-rebaseline</t>
+  </si>
+  <si>
+    <t>NEEDS-VERIFY</t>
+  </si>
+  <si>
+    <t>PR #1264 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>AF-1-entity-coa-fix</t>
+  </si>
+  <si>
+    <t>PR #530 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>AF-2-qbo-drift</t>
+  </si>
+  <si>
+    <t>PR #532 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>AF-3-account-registers</t>
+  </si>
+  <si>
+    <t>PR #534 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>AF-4-ap-bills-migration</t>
+  </si>
+  <si>
+    <t>PR #536 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>AF-6-finance-hub</t>
+  </si>
+  <si>
+    <t>PR #540 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>AF-7-money-controls</t>
+  </si>
+  <si>
+    <t>PR #542 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>AF-8-payroll-bridge</t>
+  </si>
+  <si>
+    <t>PR #544 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BK7-INLINE-CREATE-DRAWERS</t>
+  </si>
+  <si>
+    <t>PR #866 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-04-of-29-TIER2-RATE-LIMIT</t>
+  </si>
+  <si>
+    <t>PR #1189 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-05-of-29-TIER2-CIRCUIT-BREAKERS</t>
+  </si>
+  <si>
+    <t>PR #1192 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-06-of-29-TIER2-OUTBOX-DLQ</t>
+  </si>
+  <si>
+    <t>PR #1196 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-08-of-29-TIER2-LOAD-TEST</t>
+  </si>
+  <si>
+    <t>PR #796 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-09-of-29-TIER2-E2E-PATHS</t>
+  </si>
+  <si>
+    <t>PR #802 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-10-account-balances</t>
+  </si>
+  <si>
+    <t>accounting</t>
+  </si>
+  <si>
+    <t>PR #1224 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-10-of-29-TIER2-RLS-TEST-GATE</t>
+  </si>
+  <si>
+    <t>BLOCK-11-of-29-TIER2-AUDIT-COVERAGE</t>
+  </si>
+  <si>
+    <t>PR #814 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-13-of-29-TIER2-TUNING-CATALOG</t>
+  </si>
+  <si>
+    <t>PR #794 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-14-of-29-TIER2.5-MEXICO-OPS</t>
+  </si>
+  <si>
+    <t>PR #804 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-15-of-29-TIER2.5-MECHANIC-SHOP</t>
+  </si>
+  <si>
+    <t>PR #805 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-16-of-29-TIER2.5-FUEL-CARD</t>
+  </si>
+  <si>
+    <t>PR #701 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-20-cash-basis</t>
+  </si>
+  <si>
+    <t>PR #806 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-20-frontend-selector</t>
+  </si>
+  <si>
+    <t>BLOCK-20-of-29-TIER3-SECRETS-ROTATION</t>
+  </si>
+  <si>
+    <t>block-20-period-close-lock</t>
+  </si>
+  <si>
+    <t>block-21-expense-category-map</t>
+  </si>
+  <si>
+    <t>PR #807 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-21-of-29-TIER3-DR-DRILL</t>
+  </si>
+  <si>
+    <t>block-22-driver-settlement-engine</t>
+  </si>
+  <si>
+    <t>PR #241 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-22-of-29-TIER3-OPS-RUNBOOKS</t>
+  </si>
+  <si>
+    <t>block-23-escrow-posting-flow</t>
+  </si>
+  <si>
+    <t>PR #808 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-23-of-29-TIER3-DEGRADATION</t>
+  </si>
+  <si>
+    <t>block-24-factoring-posting</t>
+  </si>
+  <si>
+    <t>PR #214 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-25-factoring-fees-reserves</t>
+  </si>
+  <si>
+    <t>PR #216 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-26-factoring-reconciliation</t>
+  </si>
+  <si>
+    <t>PR #809 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-26-of-29-TIER4-PARTITION</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>block-27-fuel-expense-posting</t>
+  </si>
+  <si>
+    <t>PR #810 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-27-of-29-TIER4-CANARY</t>
+  </si>
+  <si>
+    <t>block-28-maintenance-ap-posting</t>
+  </si>
+  <si>
+    <t>PR #811 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-28-of-29-TIER4-VENDOR-LOCKIN</t>
+  </si>
+  <si>
+    <t>block-29-bank-reconciliation-engine</t>
+  </si>
+  <si>
+    <t>PR #813 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-29-of-29-TIER4-KNOWN-LIMITATIONS</t>
+  </si>
+  <si>
+    <t>block-30-bank-reconciliation-ui</t>
+  </si>
+  <si>
+    <t>PR #219 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-31-sales-tax-handling</t>
+  </si>
+  <si>
+    <t>PR #222 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-33-invoice-line-revenue-mapping</t>
+  </si>
+  <si>
+    <t>PR #209 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-34-payment-application</t>
+  </si>
+  <si>
+    <t>claimed built 2026-06-24 — no branch/signature-file evidence; GUARD must verify</t>
+  </si>
+  <si>
+    <t>block-35-chart-of-accounts-roles</t>
+  </si>
+  <si>
+    <t>block-36-multi-entity-accounting</t>
+  </si>
+  <si>
+    <t>PR #225 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-37-qbo-sync-repair-pipeline</t>
+  </si>
+  <si>
+    <t>PR #226 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-40-accounting-audit-trail</t>
+  </si>
+  <si>
+    <t>PR #227 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-41-posting-lineage-ui</t>
+  </si>
+  <si>
+    <t>PR #228 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-43-live-db-schema-verification</t>
+  </si>
+  <si>
+    <t>PR #232 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-cf-cash-forecast</t>
+  </si>
+  <si>
+    <t>PR #698 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-cmc-month-close-wizard</t>
+  </si>
+  <si>
+    <t>BLOCK-I-CI-DIST-FIX</t>
+  </si>
+  <si>
+    <t>PR #73 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>BLOCK-J-MASTER-DATA-GRANT</t>
+  </si>
+  <si>
+    <t>PR #1063 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>block-ppc-period-comparison</t>
+  </si>
+  <si>
+    <t>PR #1060 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>CAP-AUTOSTATUS</t>
+  </si>
+  <si>
+    <t>doc self-reports "✅ DONE — verify only (CAP-4 auto-status, PR #223, row 101).", unverified</t>
+  </si>
+  <si>
+    <t>CAP-CARGOTEMP</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY — reefer shipped #942/#1218; confirm cargo-TEMP gap only.", unver</t>
+  </si>
+  <si>
+    <t>CAP-ENGINEWO</t>
+  </si>
+  <si>
+    <t>doc self-reports "✅ DONE — verify only (CAP-8 engine→WO, PR #229, row 105).", unverified</t>
+  </si>
+  <si>
+    <t>CAP-FUELFRAUD</t>
+  </si>
+  <si>
+    <t>doc self-reports "✅ DONE adjacent — verify (CAP-FUEL-CARD, PR #237, row 117).", unverified</t>
+  </si>
+  <si>
+    <t>CAP-GPS</t>
+  </si>
+  <si>
+    <t>doc self-reports "✅ DONE — verify only (CAP-1 GPS, PR #234, row 98). Do NOT rebuild.", unv</t>
+  </si>
+  <si>
+    <t>CAP-PREDICTIVE</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY — CAP-7 #221 + PM auto-WO; confirm tire/brake gap only.", unverif</t>
+  </si>
+  <si>
+    <t>CAP-SCORING</t>
+  </si>
+  <si>
+    <t>doc self-reports "✅ DONE — verify only (CAP-10 driver scoring, PR #230, row 107).", unveri</t>
+  </si>
+  <si>
+    <t>CHAIN-01-vendor-picker-fix</t>
+  </si>
+  <si>
+    <t>PR #1262 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>CHAIN-03-create-bill-gl-autopost</t>
+  </si>
+  <si>
+    <t>PR #1300 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>CHAIN-04-bill-payment-tieout</t>
+  </si>
+  <si>
+    <t>PR #1267 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>CHAIN-05-bank-feed-live-proof</t>
+  </si>
+  <si>
+    <t>PR #1268 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>CHAIN-06-invoice-ar-chain-proof</t>
+  </si>
+  <si>
+    <t>PR #1269 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>CHAIN-07-settlements-500-fix</t>
+  </si>
+  <si>
+    <t>PR #1270 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>CONN-2-factoring-faro</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY — factoring #904 + FACT-1..5 shipped; confirm only the Faro packe</t>
+  </si>
+  <si>
+    <t>CONN-3-relay-internal-bank</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY-STATE (design-done #956). Tier 1 on posting. STOPS for Jorge.", u</t>
+  </si>
+  <si>
+    <t>DISP-KANBAN-dispatch-kanban-board</t>
+  </si>
+  <si>
+    <t>doc self-reports "✅ DONE — verify only (kanban, PR #751 + #1107, row 569).", unverified</t>
+  </si>
+  <si>
+    <t>DISP-OVERVIEW-dispatch-overview</t>
+  </si>
+  <si>
+    <t>doc self-reports "✅ DONE — verify only (overview, PR #752 + #1106, row 567).", unverified</t>
+  </si>
+  <si>
+    <t>DISP-PROFIT-load-profitability</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY — lane profit #375 + W2A #871; confirm per-LOAD gap only.", unver</t>
+  </si>
+  <si>
+    <t>FH-VERIFY-finance-hub-modules</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY+FLAG. Do NOT rebuild built-gated modules. Flag-ON = Tier 1, STOPS</t>
+  </si>
+  <si>
+    <t>gap-37-equipment-dual-confirm-transfer</t>
+  </si>
+  <si>
+    <t>spec self-reports shipped/merged, unverified</t>
+  </si>
+  <si>
+    <t>gap-54-wf-051-250-foot-correction</t>
+  </si>
+  <si>
+    <t>gap-65-owner-todays-attention</t>
+  </si>
+  <si>
+    <t>gap-67-accounting-home-view</t>
+  </si>
+  <si>
+    <t>gap-68-safety-officer-home-view</t>
+  </si>
+  <si>
+    <t>gap-69-driver-manager-home-view</t>
+  </si>
+  <si>
+    <t>gap-81-drug-alcohol-program</t>
+  </si>
+  <si>
+    <t>gap-87-audit-log-viewer</t>
+  </si>
+  <si>
+    <t>HOS-VIEWER-DONE</t>
+  </si>
+  <si>
+    <t>doc self-reports "DONE — shipped + GUARD-verified live 2026-06-19. Tracked here so it is N</t>
+  </si>
+  <si>
+    <t>INS-MODULE</t>
+  </si>
+  <si>
+    <t>doc self-reports "✅ DONE — verify only (insurance INS-01..07, #314–335, rows 242–248).", u</t>
+  </si>
+  <si>
+    <t>MNT-SHOP</t>
+  </si>
+  <si>
+    <t>doc self-reports "✅ DONE — verify only (mechanic shop, PR #805, row 595).", unverified</t>
+  </si>
+  <si>
+    <t>MX-OPS</t>
+  </si>
+  <si>
+    <t>doc self-reports "✅ DONE — verify only (Mexico ops, PR #804, row 594).", unverified</t>
+  </si>
+  <si>
+    <t>PREREQ-A-SCHEMA-GRANT-GATE</t>
+  </si>
+  <si>
+    <t>PR #684 title-match only, unverified</t>
+  </si>
+  <si>
+    <t>RPT-MODULE</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY — reports foundation #155/#264 shipped; find missing reports only</t>
+  </si>
+  <si>
+    <t>SAFE-W3</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY — W3 shipped #877–883; safety module LOCKED (CLAUDE.md §7).", unv</t>
+  </si>
+  <si>
+    <t>SAFE-W4</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY — W4 shipped #877–883; safety module LOCKED (CLAUDE.md §7).", unv</t>
+  </si>
+  <si>
+    <t>SAFE-W5</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY — W5 shipped #877–883; safety module LOCKED (CLAUDE.md §7).", unv</t>
+  </si>
+  <si>
+    <t>UX-A-table-alignment-DONE</t>
+  </si>
+  <si>
+    <t>doc self-reports "DONE (partial). Logic correct on the shared DataTable (Drivers list): te</t>
+  </si>
+  <si>
+    <t>VOID-VERIFY-void-everywhere</t>
+  </si>
+  <si>
+    <t>doc self-reports "VERIFY+FLAG. Do NOT rebuild built-gated. Flag-ON = Tier 1, STOPS for Jor</t>
+  </si>
+  <si>
     <t>A1-AUDIT-SPINE-LINK-COLUMNS</t>
   </si>
   <si>
@@ -527,288 +1040,42 @@
     <t>PR #815 merged 2026-06-08</t>
   </si>
   <si>
-    <t>AF-0-rebaseline</t>
-  </si>
-  <si>
-    <t>PR #1264 (title match)</t>
-  </si>
-  <si>
-    <t>AF-1-entity-coa-fix</t>
-  </si>
-  <si>
-    <t>PR #530 (title match)</t>
-  </si>
-  <si>
-    <t>AF-2-qbo-drift</t>
-  </si>
-  <si>
-    <t>PR #532 (title match)</t>
-  </si>
-  <si>
-    <t>AF-3-account-registers</t>
-  </si>
-  <si>
-    <t>PR #534 (title match)</t>
-  </si>
-  <si>
-    <t>AF-4-ap-bills-migration</t>
-  </si>
-  <si>
-    <t>PR #536 (title match)</t>
-  </si>
-  <si>
-    <t>AF-6-finance-hub</t>
-  </si>
-  <si>
-    <t>PR #540 (title match)</t>
-  </si>
-  <si>
-    <t>AF-7-money-controls</t>
-  </si>
-  <si>
-    <t>PR #542 (title match)</t>
-  </si>
-  <si>
-    <t>AF-8-payroll-bridge</t>
-  </si>
-  <si>
-    <t>PR #544 (title match)</t>
-  </si>
-  <si>
-    <t>BK7-INLINE-CREATE-DRAWERS</t>
-  </si>
-  <si>
-    <t>PR #866 (title match) merged 2026-06-11</t>
-  </si>
-  <si>
-    <t>BLOCK-04-of-29-TIER2-RATE-LIMIT</t>
-  </si>
-  <si>
-    <t>PR #1189 (title match)</t>
-  </si>
-  <si>
-    <t>BLOCK-05-of-29-TIER2-CIRCUIT-BREAKERS</t>
-  </si>
-  <si>
-    <t>PR #1192 (title match)</t>
-  </si>
-  <si>
     <t>BLOCK-05-TIER2-CIRCUIT-BREAKERS</t>
   </si>
   <si>
     <t>PR #800 merged 2026-06-08</t>
   </si>
   <si>
-    <t>BLOCK-06-of-29-TIER2-OUTBOX-DLQ</t>
-  </si>
-  <si>
-    <t>PR #1196 (title match)</t>
-  </si>
-  <si>
-    <t>BLOCK-08-of-29-TIER2-LOAD-TEST</t>
-  </si>
-  <si>
-    <t>PR #796 (title match)</t>
-  </si>
-  <si>
     <t>BLOCK-08-TIER2-LOAD-TEST</t>
   </si>
   <si>
     <t>PR #796 merged 2026-06-08</t>
   </si>
   <si>
-    <t>BLOCK-09-of-29-TIER2-E2E-PATHS</t>
-  </si>
-  <si>
-    <t>PR #802 (title match)</t>
-  </si>
-  <si>
     <t>BLOCK-09-TIER2-E2E-PATHS</t>
   </si>
   <si>
     <t>PR #802 merged 2026-06-09</t>
   </si>
   <si>
-    <t>block-10-account-balances</t>
-  </si>
-  <si>
-    <t>accounting</t>
-  </si>
-  <si>
-    <t>financial posting engine — verified built 2026-06-24</t>
-  </si>
-  <si>
-    <t>BLOCK-10-of-29-TIER2-RLS-TEST-GATE</t>
-  </si>
-  <si>
-    <t>PR #1224 (title match)</t>
-  </si>
-  <si>
     <t>BLOCK-10-TIER2-RLS-TEST-GATE</t>
   </si>
   <si>
     <t>PR #801 merged 2026-06-09</t>
   </si>
   <si>
-    <t>BLOCK-11-of-29-TIER2-AUDIT-COVERAGE</t>
-  </si>
-  <si>
-    <t>PR #814 (title match)</t>
-  </si>
-  <si>
-    <t>BLOCK-13-of-29-TIER2-TUNING-CATALOG</t>
-  </si>
-  <si>
-    <t>PR #794 (title match)</t>
-  </si>
-  <si>
     <t>BLOCK-13-TIER2-TUNING-CATALOG</t>
   </si>
   <si>
     <t>PR #794 merged 2026-06-08</t>
   </si>
   <si>
-    <t>BLOCK-14-of-29-TIER2.5-MEXICO-OPS</t>
-  </si>
-  <si>
-    <t>PR #804 (title match)</t>
-  </si>
-  <si>
-    <t>BLOCK-15-of-29-TIER2.5-MECHANIC-SHOP</t>
-  </si>
-  <si>
-    <t>PR #805 (title match)</t>
-  </si>
-  <si>
     <t>BLOCK-16-COMPLIANCE-DASHBOARD</t>
   </si>
   <si>
     <t>PR #701 merged 2026-06-07</t>
   </si>
   <si>
-    <t>BLOCK-16-of-29-TIER2.5-FUEL-CARD</t>
-  </si>
-  <si>
-    <t>PR #701 (title match)</t>
-  </si>
-  <si>
-    <t>block-20-cash-basis</t>
-  </si>
-  <si>
-    <t>block-20-frontend-selector</t>
-  </si>
-  <si>
-    <t>BLOCK-20-of-29-TIER3-SECRETS-ROTATION</t>
-  </si>
-  <si>
-    <t>PR #806 (title match)</t>
-  </si>
-  <si>
-    <t>block-20-period-close-lock</t>
-  </si>
-  <si>
-    <t>block-21-expense-category-map</t>
-  </si>
-  <si>
-    <t>BLOCK-21-of-29-TIER3-DR-DRILL</t>
-  </si>
-  <si>
-    <t>PR #807 (title match)</t>
-  </si>
-  <si>
-    <t>block-22-driver-settlement-engine</t>
-  </si>
-  <si>
-    <t>BLOCK-22-of-29-TIER3-OPS-RUNBOOKS</t>
-  </si>
-  <si>
-    <t>PR #241 (title match)</t>
-  </si>
-  <si>
-    <t>block-23-escrow-posting-flow</t>
-  </si>
-  <si>
-    <t>BLOCK-23-of-29-TIER3-DEGRADATION</t>
-  </si>
-  <si>
-    <t>PR #808 (title match)</t>
-  </si>
-  <si>
-    <t>block-24-factoring-posting</t>
-  </si>
-  <si>
-    <t>block-25-factoring-fees-reserves</t>
-  </si>
-  <si>
-    <t>block-26-factoring-reconciliation</t>
-  </si>
-  <si>
-    <t>BLOCK-26-of-29-TIER4-PARTITION</t>
-  </si>
-  <si>
-    <t>T4</t>
-  </si>
-  <si>
-    <t>PR #809 (title match)</t>
-  </si>
-  <si>
-    <t>block-27-fuel-expense-posting</t>
-  </si>
-  <si>
-    <t>BLOCK-27-of-29-TIER4-CANARY</t>
-  </si>
-  <si>
-    <t>PR #810 (title match)</t>
-  </si>
-  <si>
-    <t>block-28-maintenance-ap-posting</t>
-  </si>
-  <si>
-    <t>BLOCK-28-of-29-TIER4-VENDOR-LOCKIN</t>
-  </si>
-  <si>
-    <t>PR #811 (title match)</t>
-  </si>
-  <si>
-    <t>block-29-bank-reconciliation-engine</t>
-  </si>
-  <si>
-    <t>BLOCK-29-of-29-TIER4-KNOWN-LIMITATIONS</t>
-  </si>
-  <si>
-    <t>PR #813 (title match)</t>
-  </si>
-  <si>
-    <t>block-30-bank-reconciliation-ui</t>
-  </si>
-  <si>
-    <t>block-31-sales-tax-handling</t>
-  </si>
-  <si>
-    <t>block-33-invoice-line-revenue-mapping</t>
-  </si>
-  <si>
-    <t>block-34-payment-application</t>
-  </si>
-  <si>
-    <t>block-35-chart-of-accounts-roles</t>
-  </si>
-  <si>
-    <t>block-36-multi-entity-accounting</t>
-  </si>
-  <si>
-    <t>block-37-qbo-sync-repair-pipeline</t>
-  </si>
-  <si>
-    <t>block-40-accounting-audit-trail</t>
-  </si>
-  <si>
-    <t>block-41-posting-lineage-ui</t>
-  </si>
-  <si>
-    <t>block-43-live-db-schema-verification</t>
-  </si>
-  <si>
     <t>BLOCK-C-DEDUCTION-CAP</t>
   </si>
   <si>
@@ -821,12 +1088,6 @@
     <t>PR #698 merged 2026-06-07</t>
   </si>
   <si>
-    <t>block-cf-cash-forecast</t>
-  </si>
-  <si>
-    <t>block-cmc-month-close-wizard</t>
-  </si>
-  <si>
     <t>BLOCK-D-INSURANCE-RENEWAL</t>
   </si>
   <si>
@@ -857,21 +1118,6 @@
     <t>PR #693 merged 2026-06-07</t>
   </si>
   <si>
-    <t>BLOCK-I-CI-DIST-FIX</t>
-  </si>
-  <si>
-    <t>PR #73 (title match) merged 2026-05-15</t>
-  </si>
-  <si>
-    <t>BLOCK-J-MASTER-DATA-GRANT</t>
-  </si>
-  <si>
-    <t>PR #1063 (title match) merged 2026-06-16</t>
-  </si>
-  <si>
-    <t>block-ppc-period-comparison</t>
-  </si>
-  <si>
     <t>BLOCK5-INSURANCE-FORWARD-FIX</t>
   </si>
   <si>
@@ -926,84 +1172,6 @@
     <t>all 10 file(s) on main</t>
   </si>
   <si>
-    <t>CAP-AUTOSTATUS</t>
-  </si>
-  <si>
-    <t>✅ DONE — verify only (CAP-4 auto-status, PR #223, row 101).</t>
-  </si>
-  <si>
-    <t>CAP-CARGOTEMP</t>
-  </si>
-  <si>
-    <t>VERIFY — reefer shipped #942/#1218; confirm cargo-TEMP gap only.</t>
-  </si>
-  <si>
-    <t>CAP-ENGINEWO</t>
-  </si>
-  <si>
-    <t>✅ DONE — verify only (CAP-8 engine→WO, PR #229, row 105).</t>
-  </si>
-  <si>
-    <t>CAP-FUELFRAUD</t>
-  </si>
-  <si>
-    <t>✅ DONE adjacent — verify (CAP-FUEL-CARD, PR #237, row 117).</t>
-  </si>
-  <si>
-    <t>CAP-GPS</t>
-  </si>
-  <si>
-    <t>✅ DONE — verify only (CAP-1 GPS, PR #234, row 98). Do NOT rebuild.</t>
-  </si>
-  <si>
-    <t>CAP-PREDICTIVE</t>
-  </si>
-  <si>
-    <t>VERIFY — CAP-7 #221 + PM auto-WO; confirm tire/brake gap only.</t>
-  </si>
-  <si>
-    <t>CAP-SCORING</t>
-  </si>
-  <si>
-    <t>✅ DONE — verify only (CAP-10 driver scoring, PR #230, row 107).</t>
-  </si>
-  <si>
-    <t>CHAIN-01-vendor-picker-fix</t>
-  </si>
-  <si>
-    <t>PR #1262 (title match)</t>
-  </si>
-  <si>
-    <t>CHAIN-03-create-bill-gl-autopost</t>
-  </si>
-  <si>
-    <t>PR #1300 (title match)</t>
-  </si>
-  <si>
-    <t>CHAIN-04-bill-payment-tieout</t>
-  </si>
-  <si>
-    <t>PR #1267 (title match)</t>
-  </si>
-  <si>
-    <t>CHAIN-05-bank-feed-live-proof</t>
-  </si>
-  <si>
-    <t>PR #1268 (title match)</t>
-  </si>
-  <si>
-    <t>CHAIN-06-invoice-ar-chain-proof</t>
-  </si>
-  <si>
-    <t>PR #1269 (title match)</t>
-  </si>
-  <si>
-    <t>CHAIN-07-settlements-500-fix</t>
-  </si>
-  <si>
-    <t>PR #1270 (title match)</t>
-  </si>
-  <si>
     <t>CHORE-MASTER-TRACKER-MD</t>
   </si>
   <si>
@@ -1094,18 +1262,6 @@
     <t>PR #789 merged 2026-06-10</t>
   </si>
   <si>
-    <t>CONN-2-factoring-faro</t>
-  </si>
-  <si>
-    <t>VERIFY — factoring #904 + FACT-1..5 shipped; confirm only the Faro packet gap.</t>
-  </si>
-  <si>
-    <t>CONN-3-relay-internal-bank</t>
-  </si>
-  <si>
-    <t>VERIFY-STATE (design-done #956). Tier 1 on posting. STOPS for Jorge.</t>
-  </si>
-  <si>
     <t>D1-SETTLEMENTS-APPROVAL-PDF</t>
   </si>
   <si>
@@ -1136,12 +1292,6 @@
     <t>PR #762 merged 2026-06-08</t>
   </si>
   <si>
-    <t>DISP-KANBAN-dispatch-kanban-board</t>
-  </si>
-  <si>
-    <t>✅ DONE — verify only (kanban, PR #751 + #1107, row 569).</t>
-  </si>
-  <si>
     <t>DISP-KANBAN-STATES</t>
   </si>
   <si>
@@ -1160,24 +1310,12 @@
     <t>PR #752 merged 2026-06-08</t>
   </si>
   <si>
-    <t>DISP-OVERVIEW-dispatch-overview</t>
-  </si>
-  <si>
-    <t>✅ DONE — verify only (overview, PR #752 + #1106, row 567).</t>
-  </si>
-  <si>
     <t>DISP-PLANNERS</t>
   </si>
   <si>
     <t>all 11 file(s) on main</t>
   </si>
   <si>
-    <t>DISP-PROFIT-load-profitability</t>
-  </si>
-  <si>
-    <t>VERIFY — lane profit #375 + W2A #871; confirm per-LOAD gap only.</t>
-  </si>
-  <si>
     <t>DISP-PROFITABILITY</t>
   </si>
   <si>
@@ -1637,12 +1775,6 @@
     <t>PR #977 merged 2026-06-15</t>
   </si>
   <si>
-    <t>FH-VERIFY-finance-hub-modules</t>
-  </si>
-  <si>
-    <t>VERIFY+FLAG. Do NOT rebuild built-gated modules. Flag-ON = Tier 1, STOPS for Jorge.</t>
-  </si>
-  <si>
     <t>FIX-AT-RISK-LOADS-SD-CITY</t>
   </si>
   <si>
@@ -1907,12 +2039,6 @@
     <t>PR #765 merged 2026-06-08</t>
   </si>
   <si>
-    <t>gap-37-equipment-dual-confirm-transfer</t>
-  </si>
-  <si>
-    <t>spec marks shipped/merged</t>
-  </si>
-  <si>
     <t>GAP-38-DAMAGE-INSURANCE-CONTINUITY</t>
   </si>
   <si>
@@ -2015,9 +2141,6 @@
     <t>PR #775 merged 2026-06-08</t>
   </si>
   <si>
-    <t>gap-54-wf-051-250-foot-correction</t>
-  </si>
-  <si>
     <t>GAP-55</t>
   </si>
   <si>
@@ -2078,9 +2201,6 @@
     <t>PR #783 merged 2026-06-08</t>
   </si>
   <si>
-    <t>gap-65-owner-todays-attention</t>
-  </si>
-  <si>
     <t>GAP-66-DISPATCHER-HOME</t>
   </si>
   <si>
@@ -2093,27 +2213,18 @@
     <t>PR #652 merged 2026-06-07</t>
   </si>
   <si>
-    <t>gap-67-accounting-home-view</t>
-  </si>
-  <si>
     <t>GAP-68-SAFETY-OFFICER-HOME</t>
   </si>
   <si>
     <t>PR #653 merged 2026-06-07</t>
   </si>
   <si>
-    <t>gap-68-safety-officer-home-view</t>
-  </si>
-  <si>
     <t>GAP-69-DRIVER-MANAGER-HOME</t>
   </si>
   <si>
     <t>PR #654 merged 2026-06-07</t>
   </si>
   <si>
-    <t>gap-69-driver-manager-home-view</t>
-  </si>
-  <si>
     <t>GAP-7</t>
   </si>
   <si>
@@ -2147,9 +2258,6 @@
     <t>PR #661 merged 2026-06-07</t>
   </si>
   <si>
-    <t>gap-81-drug-alcohol-program</t>
-  </si>
-  <si>
     <t>GAP-82-MEDICAL-CARD-TRACKING</t>
   </si>
   <si>
@@ -2183,9 +2291,6 @@
     <t>GAP-86-POLICY-WIZARD</t>
   </si>
   <si>
-    <t>gap-87-audit-log-viewer</t>
-  </si>
-  <si>
     <t>GAP-89-UNIVERSAL-SEARCH-CMD-K</t>
   </si>
   <si>
@@ -2237,24 +2342,12 @@
     <t>PR #723 merged 2026-06-08</t>
   </si>
   <si>
-    <t>HOS-VIEWER-DONE</t>
-  </si>
-  <si>
-    <t>DONE — shipped + GUARD-verified live 2026-06-19. Tracked here so it is NOT re-opened.</t>
-  </si>
-  <si>
     <t>HOTFIX-0327-MIGRATION-ROLE</t>
   </si>
   <si>
     <t>PR #643 merged 2026-06-07</t>
   </si>
   <si>
-    <t>INS-MODULE</t>
-  </si>
-  <si>
-    <t>✅ DONE — verify only (insurance INS-01..07, #314–335, rows 242–248).</t>
-  </si>
-  <si>
     <t>ITEM1-TWO-SIDED-ITEM</t>
   </si>
   <si>
@@ -2285,18 +2378,6 @@
     <t>PR #914 merged 2026-06-13</t>
   </si>
   <si>
-    <t>MNT-SHOP</t>
-  </si>
-  <si>
-    <t>✅ DONE — verify only (mechanic shop, PR #805, row 595).</t>
-  </si>
-  <si>
-    <t>MX-OPS</t>
-  </si>
-  <si>
-    <t>✅ DONE — verify only (Mexico ops, PR #804, row 594).</t>
-  </si>
-  <si>
     <t>OB1-NAV-HEADER-UNIFY</t>
   </si>
   <si>
@@ -2315,42 +2396,12 @@
     <t>PR #862 merged 2026-06-10</t>
   </si>
   <si>
-    <t>PREREQ-A-SCHEMA-GRANT-GATE</t>
-  </si>
-  <si>
-    <t>PR #684 (title match) merged 2026-06-07</t>
-  </si>
-  <si>
     <t>PREREQ-B-SETTLEMENT-DEDUCTION-SVC</t>
   </si>
   <si>
     <t>PR #683 merged 2026-06-07</t>
   </si>
   <si>
-    <t>RPT-MODULE</t>
-  </si>
-  <si>
-    <t>VERIFY — reports foundation #155/#264 shipped; find missing reports only.</t>
-  </si>
-  <si>
-    <t>SAFE-W3</t>
-  </si>
-  <si>
-    <t>VERIFY — W3 shipped #877–883; safety module LOCKED (CLAUDE.md §7).</t>
-  </si>
-  <si>
-    <t>SAFE-W4</t>
-  </si>
-  <si>
-    <t>VERIFY — W4 shipped #877–883; safety module LOCKED (CLAUDE.md §7).</t>
-  </si>
-  <si>
-    <t>SAFE-W5</t>
-  </si>
-  <si>
-    <t>VERIFY — W5 shipped #877–883; safety module LOCKED (CLAUDE.md §7).</t>
-  </si>
-  <si>
     <t>SETTLEMENTS-SIDEBAR-RENAME-MOVE</t>
   </si>
   <si>
@@ -2457,18 +2508,6 @@
   </si>
   <si>
     <t>PR #813 merged 2026-06-08</t>
-  </si>
-  <si>
-    <t>UX-A-table-alignment-DONE</t>
-  </si>
-  <si>
-    <t>DONE (partial). Logic correct on the shared DataTable (Drivers list): text/title centered,</t>
-  </si>
-  <si>
-    <t>VOID-VERIFY-void-everywhere</t>
-  </si>
-  <si>
-    <t>VERIFY+FLAG. Do NOT rebuild built-gated. Flag-ON = Tier 1, STOPS for Jorge.</t>
   </si>
   <si>
     <t>W1-EVENT-LOG-SPINE</t>
@@ -2585,7 +2624,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2614,6 +2653,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE6F4EA"/>
       </patternFill>
     </fill>
@@ -2630,7 +2674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2647,6 +2691,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4771,10 +4818,10 @@
         <v>89</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>136</v>
@@ -4788,13 +4835,13 @@
         <v>135</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>138</v>
@@ -4808,13 +4855,13 @@
         <v>135</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>140</v>
@@ -4828,13 +4875,13 @@
         <v>135</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>142</v>
@@ -4848,13 +4895,13 @@
         <v>135</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>144</v>
@@ -4868,13 +4915,13 @@
         <v>135</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>146</v>
@@ -4888,13 +4935,13 @@
         <v>135</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>148</v>
@@ -4908,13 +4955,13 @@
         <v>135</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>150</v>
@@ -4951,10 +4998,10 @@
         <v>10</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>154</v>
@@ -4971,10 +5018,10 @@
         <v>10</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>156</v>
@@ -4991,10 +5038,10 @@
         <v>10</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>158</v>
@@ -5011,10 +5058,10 @@
         <v>10</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>160</v>
@@ -5031,10 +5078,10 @@
         <v>10</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>162</v>
@@ -5048,21 +5095,21 @@
         <v>135</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="105" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>135</v>
@@ -5071,13 +5118,13 @@
         <v>10</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="106" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -5091,10 +5138,10 @@
         <v>10</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>168</v>
@@ -5111,10 +5158,10 @@
         <v>10</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>170</v>
@@ -5128,13 +5175,13 @@
         <v>135</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>172</v>
@@ -5148,13 +5195,13 @@
         <v>135</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>174</v>
@@ -5168,13 +5215,13 @@
         <v>135</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>176</v>
@@ -5191,10 +5238,10 @@
         <v>89</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>178</v>
@@ -5211,38 +5258,38 @@
         <v>89</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="113" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="114" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>135</v>
@@ -5251,18 +5298,18 @@
         <v>89</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="115" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>135</v>
@@ -5271,18 +5318,18 @@
         <v>89</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="116" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>135</v>
@@ -5291,38 +5338,38 @@
         <v>10</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="117" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="118" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>135</v>
@@ -5331,38 +5378,38 @@
         <v>10</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="119" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="120" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>135</v>
@@ -5371,78 +5418,78 @@
         <v>10</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="121" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="122" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="123" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="124" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>135</v>
@@ -5451,18 +5498,18 @@
         <v>10</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>135</v>
@@ -5474,15 +5521,15 @@
         <v>10</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="126" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>135</v>
@@ -5491,38 +5538,38 @@
         <v>10</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="127" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="128" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>135</v>
@@ -5531,38 +5578,38 @@
         <v>10</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="129" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
     </row>
     <row r="130" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>135</v>
@@ -5571,98 +5618,98 @@
         <v>10</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
     <row r="131" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="132" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="133" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="134" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="135" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>135</v>
@@ -5674,15 +5721,15 @@
         <v>10</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="136" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>135</v>
@@ -5694,35 +5741,35 @@
         <v>10</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="137" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
     </row>
     <row r="138" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>135</v>
@@ -5734,15 +5781,15 @@
         <v>10</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
     </row>
     <row r="139" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>135</v>
@@ -5754,35 +5801,35 @@
         <v>10</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="140" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>135</v>
@@ -5794,55 +5841,55 @@
         <v>10</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
     </row>
     <row r="142" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>12</v>
+        <v>164</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="143" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>206</v>
+        <v>18</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
     </row>
     <row r="144" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>135</v>
@@ -5851,18 +5898,18 @@
         <v>10</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="145" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>135</v>
@@ -5874,55 +5921,55 @@
         <v>10</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
     </row>
     <row r="146" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
     </row>
     <row r="147" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
     </row>
     <row r="148" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>135</v>
@@ -5931,38 +5978,38 @@
         <v>10</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="149" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
     </row>
     <row r="150" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>135</v>
@@ -5971,38 +6018,38 @@
         <v>10</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="151" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
     </row>
     <row r="152" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>135</v>
@@ -6011,18 +6058,18 @@
         <v>10</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="153" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>135</v>
@@ -6031,38 +6078,38 @@
         <v>89</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>207</v>
+        <v>251</v>
       </c>
     </row>
     <row r="154" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>244</v>
+        <v>96</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="155" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>135</v>
@@ -6071,13 +6118,13 @@
         <v>89</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>207</v>
+        <v>255</v>
       </c>
     </row>
     <row r="156" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -6091,18 +6138,18 @@
         <v>89</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>207</v>
+        <v>257</v>
       </c>
     </row>
     <row r="157" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>135</v>
@@ -6111,18 +6158,18 @@
         <v>89</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
     </row>
     <row r="158" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>135</v>
@@ -6131,18 +6178,18 @@
         <v>89</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>207</v>
+        <v>261</v>
       </c>
     </row>
     <row r="159" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>135</v>
@@ -6154,15 +6201,15 @@
         <v>10</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>207</v>
+        <v>263</v>
       </c>
     </row>
     <row r="160" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>135</v>
@@ -6171,78 +6218,78 @@
         <v>89</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>207</v>
+        <v>265</v>
       </c>
     </row>
     <row r="161" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
     </row>
     <row r="162" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>207</v>
+        <v>269</v>
       </c>
     </row>
     <row r="163" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>207</v>
+        <v>271</v>
       </c>
     </row>
     <row r="164" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>135</v>
@@ -6251,18 +6298,18 @@
         <v>89</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>207</v>
+        <v>273</v>
       </c>
     </row>
     <row r="165" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>135</v>
@@ -6274,15 +6321,15 @@
         <v>10</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="166" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>135</v>
@@ -6294,55 +6341,55 @@
         <v>10</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
     </row>
     <row r="168" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
     </row>
     <row r="169" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>135</v>
@@ -6354,15 +6401,15 @@
         <v>10</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="170" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>135</v>
@@ -6374,15 +6421,15 @@
         <v>10</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="171" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>135</v>
@@ -6394,15 +6441,15 @@
         <v>10</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="172" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>135</v>
@@ -6414,15 +6461,15 @@
         <v>10</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="173" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>135</v>
@@ -6434,15 +6481,15 @@
         <v>10</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="174" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>135</v>
@@ -6454,15 +6501,15 @@
         <v>10</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="175" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>135</v>
@@ -6474,35 +6521,35 @@
         <v>10</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="176" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>207</v>
+        <v>290</v>
       </c>
     </row>
     <row r="177" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>135</v>
@@ -6517,12 +6564,12 @@
         <v>18</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="178" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>135</v>
@@ -6534,15 +6581,15 @@
         <v>10</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="179" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>135</v>
@@ -6554,15 +6601,15 @@
         <v>10</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="180" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>135</v>
@@ -6574,15 +6621,15 @@
         <v>10</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="181" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B181" s="7" t="s">
         <v>135</v>
@@ -6594,15 +6641,15 @@
         <v>10</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="182" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B182" s="7" t="s">
         <v>135</v>
@@ -6614,38 +6661,38 @@
         <v>10</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="183" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="184" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>135</v>
+        <v>305</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>89</v>
@@ -6657,18 +6704,18 @@
         <v>18</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="185" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B185" s="7" t="s">
-        <v>135</v>
+        <v>308</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>10</v>
@@ -6677,15 +6724,15 @@
         <v>18</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="186" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>135</v>
+        <v>310</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>10</v>
@@ -6694,18 +6741,18 @@
         <v>10</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="187" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B187" s="7" t="s">
-        <v>135</v>
+        <v>312</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>10</v>
@@ -6714,18 +6761,18 @@
         <v>10</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="188" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>135</v>
+        <v>314</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>10</v>
@@ -6734,18 +6781,18 @@
         <v>10</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="189" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B189" s="7" t="s">
-        <v>135</v>
+        <v>316</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>10</v>
@@ -6754,18 +6801,18 @@
         <v>10</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="190" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>135</v>
+        <v>318</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>10</v>
@@ -6774,18 +6821,18 @@
         <v>10</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="191" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B191" s="7" t="s">
-        <v>135</v>
+        <v>320</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>10</v>
@@ -6794,18 +6841,18 @@
         <v>10</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="192" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>135</v>
+        <v>322</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>10</v>
@@ -6814,141 +6861,141 @@
         <v>10</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="193" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B193" s="7" t="s">
-        <v>135</v>
+        <v>324</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="194" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>135</v>
+        <v>326</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="195" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B195" s="7" t="s">
-        <v>135</v>
+        <v>328</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="196" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B196" s="7" t="s">
-        <v>135</v>
+        <v>330</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="197" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B197" s="7" t="s">
-        <v>135</v>
+        <v>332</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="198" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B198" s="7" t="s">
-        <v>135</v>
+        <v>334</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="199" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B199" s="7" t="s">
-        <v>135</v>
+        <v>336</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>10</v>
@@ -6957,18 +7004,18 @@
         <v>18</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="200" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B200" s="7" t="s">
-        <v>135</v>
+        <v>338</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>10</v>
@@ -6977,15 +7024,15 @@
         <v>18</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="201" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B201" s="7" t="s">
-        <v>135</v>
+        <v>340</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>10</v>
@@ -6997,15 +7044,15 @@
         <v>18</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="202" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B202" s="7" t="s">
-        <v>135</v>
+        <v>342</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>10</v>
@@ -7017,15 +7064,15 @@
         <v>18</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="203" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B203" s="7" t="s">
-        <v>135</v>
+        <v>344</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>10</v>
@@ -7037,15 +7084,15 @@
         <v>18</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="204" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>135</v>
+        <v>346</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>10</v>
@@ -7057,15 +7104,15 @@
         <v>18</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="205" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="B205" s="7" t="s">
-        <v>135</v>
+        <v>348</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>10</v>
@@ -7077,15 +7124,15 @@
         <v>18</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="206" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B206" s="7" t="s">
-        <v>135</v>
+        <v>350</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>10</v>
@@ -7097,15 +7144,15 @@
         <v>18</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="207" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B207" s="7" t="s">
-        <v>135</v>
+        <v>352</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>10</v>
@@ -7117,15 +7164,15 @@
         <v>18</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="208" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="B208" s="7" t="s">
-        <v>135</v>
+        <v>354</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>10</v>
@@ -7137,15 +7184,15 @@
         <v>18</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="209" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B209" s="7" t="s">
-        <v>135</v>
+        <v>356</v>
+      </c>
+      <c r="B209" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>10</v>
@@ -7157,15 +7204,15 @@
         <v>18</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="210" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B210" s="7" t="s">
-        <v>135</v>
+        <v>358</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>10</v>
@@ -7177,15 +7224,15 @@
         <v>18</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="211" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="B211" s="7" t="s">
-        <v>135</v>
+        <v>360</v>
+      </c>
+      <c r="B211" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>10</v>
@@ -7197,15 +7244,15 @@
         <v>18</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="212" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B212" s="7" t="s">
-        <v>135</v>
+        <v>362</v>
+      </c>
+      <c r="B212" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>10</v>
@@ -7217,15 +7264,15 @@
         <v>18</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="213" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="B213" s="7" t="s">
-        <v>135</v>
+        <v>364</v>
+      </c>
+      <c r="B213" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>10</v>
@@ -7237,55 +7284,55 @@
         <v>18</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="214" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="B214" s="7" t="s">
-        <v>135</v>
+        <v>366</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="215" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="B215" s="7" t="s">
-        <v>135</v>
+        <v>368</v>
+      </c>
+      <c r="B215" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="216" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="B216" s="7" t="s">
-        <v>135</v>
+        <v>370</v>
+      </c>
+      <c r="B216" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>10</v>
@@ -7297,15 +7344,15 @@
         <v>18</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="217" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="B217" s="7" t="s">
-        <v>135</v>
+        <v>372</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>10</v>
@@ -7317,15 +7364,15 @@
         <v>18</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="218" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B218" s="7" t="s">
-        <v>135</v>
+        <v>374</v>
+      </c>
+      <c r="B218" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>10</v>
@@ -7337,15 +7384,15 @@
         <v>18</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="219" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="B219" s="7" t="s">
-        <v>135</v>
+        <v>376</v>
+      </c>
+      <c r="B219" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>10</v>
@@ -7357,15 +7404,15 @@
         <v>18</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="220" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B220" s="7" t="s">
-        <v>135</v>
+        <v>378</v>
+      </c>
+      <c r="B220" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>10</v>
@@ -7377,15 +7424,15 @@
         <v>18</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="221" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B221" s="7" t="s">
-        <v>135</v>
+        <v>380</v>
+      </c>
+      <c r="B221" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C221" s="4" t="s">
         <v>10</v>
@@ -7394,21 +7441,21 @@
         <v>10</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="222" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B222" s="7" t="s">
-        <v>135</v>
+        <v>382</v>
+      </c>
+      <c r="B222" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>10</v>
@@ -7417,18 +7464,18 @@
         <v>18</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="223" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="B223" s="7" t="s">
-        <v>135</v>
+        <v>384</v>
+      </c>
+      <c r="B223" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D223" s="4" t="s">
         <v>10</v>
@@ -7437,18 +7484,18 @@
         <v>18</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="224" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="B224" s="7" t="s">
-        <v>135</v>
+        <v>386</v>
+      </c>
+      <c r="B224" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D224" s="4" t="s">
         <v>10</v>
@@ -7457,35 +7504,35 @@
         <v>18</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="225" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="B225" s="7" t="s">
-        <v>135</v>
+        <v>388</v>
+      </c>
+      <c r="B225" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="226" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="B226" s="7" t="s">
-        <v>135</v>
+        <v>390</v>
+      </c>
+      <c r="B226" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>10</v>
@@ -7497,15 +7544,15 @@
         <v>18</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="227" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="B227" s="7" t="s">
-        <v>135</v>
+        <v>392</v>
+      </c>
+      <c r="B227" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>10</v>
@@ -7514,18 +7561,18 @@
         <v>10</v>
       </c>
       <c r="E227" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="228" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="B228" s="7" t="s">
-        <v>135</v>
+        <v>394</v>
+      </c>
+      <c r="B228" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C228" s="4" t="s">
         <v>10</v>
@@ -7537,15 +7584,15 @@
         <v>18</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="229" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="B229" s="7" t="s">
-        <v>135</v>
+        <v>396</v>
+      </c>
+      <c r="B229" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>10</v>
@@ -7557,15 +7604,15 @@
         <v>18</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="230" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="B230" s="7" t="s">
-        <v>135</v>
+        <v>398</v>
+      </c>
+      <c r="B230" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>10</v>
@@ -7577,15 +7624,15 @@
         <v>18</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="231" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="B231" s="7" t="s">
-        <v>135</v>
+        <v>400</v>
+      </c>
+      <c r="B231" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>10</v>
@@ -7597,15 +7644,15 @@
         <v>18</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="232" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="B232" s="7" t="s">
-        <v>135</v>
+        <v>402</v>
+      </c>
+      <c r="B232" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>10</v>
@@ -7617,15 +7664,15 @@
         <v>18</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="233" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="B233" s="7" t="s">
-        <v>135</v>
+        <v>404</v>
+      </c>
+      <c r="B233" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>10</v>
@@ -7637,15 +7684,15 @@
         <v>18</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="234" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="B234" s="7" t="s">
-        <v>135</v>
+        <v>406</v>
+      </c>
+      <c r="B234" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>10</v>
@@ -7657,15 +7704,15 @@
         <v>18</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="235" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="B235" s="7" t="s">
-        <v>135</v>
+        <v>408</v>
+      </c>
+      <c r="B235" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>10</v>
@@ -7677,15 +7724,15 @@
         <v>18</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="236" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="B236" s="7" t="s">
-        <v>135</v>
+        <v>410</v>
+      </c>
+      <c r="B236" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>10</v>
@@ -7697,15 +7744,15 @@
         <v>18</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="237" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="B237" s="7" t="s">
-        <v>135</v>
+        <v>412</v>
+      </c>
+      <c r="B237" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>10</v>
@@ -7717,15 +7764,15 @@
         <v>18</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="238" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="B238" s="7" t="s">
-        <v>135</v>
+        <v>414</v>
+      </c>
+      <c r="B238" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>10</v>
@@ -7737,15 +7784,15 @@
         <v>18</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="239" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="B239" s="7" t="s">
-        <v>135</v>
+        <v>416</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>10</v>
@@ -7757,15 +7804,15 @@
         <v>18</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="240" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="B240" s="7" t="s">
-        <v>135</v>
+        <v>418</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>10</v>
@@ -7777,15 +7824,15 @@
         <v>18</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="241" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="B241" s="7" t="s">
-        <v>135</v>
+        <v>420</v>
+      </c>
+      <c r="B241" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C241" s="4" t="s">
         <v>10</v>
@@ -7797,15 +7844,15 @@
         <v>18</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="242" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="B242" s="7" t="s">
-        <v>135</v>
+        <v>422</v>
+      </c>
+      <c r="B242" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>10</v>
@@ -7817,15 +7864,15 @@
         <v>18</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="243" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="B243" s="7" t="s">
-        <v>135</v>
+        <v>424</v>
+      </c>
+      <c r="B243" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>10</v>
@@ -7837,15 +7884,15 @@
         <v>18</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="244" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="B244" s="7" t="s">
-        <v>135</v>
+        <v>426</v>
+      </c>
+      <c r="B244" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>10</v>
@@ -7857,15 +7904,15 @@
         <v>18</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="245" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="B245" s="7" t="s">
-        <v>135</v>
+        <v>428</v>
+      </c>
+      <c r="B245" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>10</v>
@@ -7877,15 +7924,15 @@
         <v>18</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="246" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="B246" s="7" t="s">
-        <v>135</v>
+        <v>430</v>
+      </c>
+      <c r="B246" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>10</v>
@@ -7897,15 +7944,15 @@
         <v>18</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="247" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="B247" s="7" t="s">
-        <v>135</v>
+        <v>432</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>10</v>
@@ -7917,15 +7964,15 @@
         <v>18</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="248" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="B248" s="7" t="s">
-        <v>135</v>
+        <v>434</v>
+      </c>
+      <c r="B248" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>10</v>
@@ -7937,15 +7984,15 @@
         <v>18</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="249" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="B249" s="7" t="s">
-        <v>135</v>
+        <v>436</v>
+      </c>
+      <c r="B249" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>10</v>
@@ -7957,15 +8004,15 @@
         <v>18</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="250" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="B250" s="7" t="s">
-        <v>135</v>
+        <v>438</v>
+      </c>
+      <c r="B250" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>10</v>
@@ -7977,15 +8024,15 @@
         <v>18</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="251" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="B251" s="7" t="s">
-        <v>135</v>
+        <v>440</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>10</v>
@@ -7997,15 +8044,15 @@
         <v>18</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="252" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="B252" s="7" t="s">
-        <v>135</v>
+        <v>442</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>10</v>
@@ -8017,15 +8064,15 @@
         <v>18</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="253" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="B253" s="7" t="s">
-        <v>135</v>
+        <v>444</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>10</v>
@@ -8037,15 +8084,15 @@
         <v>18</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="254" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="B254" s="7" t="s">
-        <v>135</v>
+        <v>446</v>
+      </c>
+      <c r="B254" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>10</v>
@@ -8057,15 +8104,15 @@
         <v>18</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="255" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="B255" s="7" t="s">
-        <v>135</v>
+        <v>448</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>10</v>
@@ -8077,15 +8124,15 @@
         <v>18</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="256" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="B256" s="7" t="s">
-        <v>135</v>
+        <v>450</v>
+      </c>
+      <c r="B256" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>10</v>
@@ -8097,15 +8144,15 @@
         <v>18</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="257" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="B257" s="7" t="s">
-        <v>135</v>
+        <v>452</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>10</v>
@@ -8117,15 +8164,15 @@
         <v>18</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="258" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="B258" s="7" t="s">
-        <v>135</v>
+        <v>454</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>10</v>
@@ -8137,15 +8184,15 @@
         <v>18</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="259" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="B259" s="7" t="s">
-        <v>135</v>
+        <v>456</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>10</v>
@@ -8157,15 +8204,15 @@
         <v>18</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="260" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="B260" s="7" t="s">
-        <v>135</v>
+        <v>458</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>10</v>
@@ -8177,15 +8224,15 @@
         <v>18</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="261" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="B261" s="7" t="s">
-        <v>135</v>
+        <v>460</v>
+      </c>
+      <c r="B261" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>10</v>
@@ -8197,15 +8244,15 @@
         <v>18</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="262" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="B262" s="7" t="s">
-        <v>135</v>
+        <v>462</v>
+      </c>
+      <c r="B262" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>10</v>
@@ -8217,15 +8264,15 @@
         <v>18</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="263" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="B263" s="7" t="s">
-        <v>135</v>
+        <v>464</v>
+      </c>
+      <c r="B263" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>10</v>
@@ -8237,15 +8284,15 @@
         <v>18</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="264" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="B264" s="7" t="s">
-        <v>135</v>
+        <v>466</v>
+      </c>
+      <c r="B264" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>10</v>
@@ -8257,18 +8304,18 @@
         <v>18</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="265" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="B265" s="7" t="s">
-        <v>135</v>
+        <v>468</v>
+      </c>
+      <c r="B265" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D265" s="4" t="s">
         <v>10</v>
@@ -8277,15 +8324,15 @@
         <v>18</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="266" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="B266" s="7" t="s">
-        <v>135</v>
+        <v>470</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>10</v>
@@ -8297,15 +8344,15 @@
         <v>18</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="267" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="B267" s="7" t="s">
-        <v>135</v>
+        <v>472</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>10</v>
@@ -8317,15 +8364,15 @@
         <v>18</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="268" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="B268" s="7" t="s">
-        <v>135</v>
+        <v>474</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>10</v>
@@ -8337,15 +8384,15 @@
         <v>18</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>369</v>
+        <v>475</v>
       </c>
     </row>
     <row r="269" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="B269" s="7" t="s">
-        <v>135</v>
+        <v>476</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C269" s="4" t="s">
         <v>10</v>
@@ -8357,15 +8404,15 @@
         <v>18</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="270" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="B270" s="7" t="s">
-        <v>135</v>
+        <v>478</v>
+      </c>
+      <c r="B270" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>10</v>
@@ -8377,18 +8424,18 @@
         <v>18</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="271" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="B271" s="7" t="s">
-        <v>135</v>
+        <v>480</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D271" s="4" t="s">
         <v>10</v>
@@ -8397,15 +8444,15 @@
         <v>18</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="272" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="B272" s="7" t="s">
-        <v>135</v>
+        <v>482</v>
+      </c>
+      <c r="B272" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>10</v>
@@ -8417,15 +8464,15 @@
         <v>18</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="273" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="B273" s="7" t="s">
-        <v>135</v>
+        <v>484</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>10</v>
@@ -8437,18 +8484,18 @@
         <v>18</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="274" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="B274" s="7" t="s">
-        <v>135</v>
+        <v>486</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D274" s="4" t="s">
         <v>10</v>
@@ -8457,18 +8504,18 @@
         <v>18</v>
       </c>
       <c r="F274" s="4" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="275" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="B275" s="7" t="s">
-        <v>135</v>
+        <v>488</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D275" s="4" t="s">
         <v>10</v>
@@ -8477,18 +8524,18 @@
         <v>18</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="276" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B276" s="7" t="s">
-        <v>135</v>
+        <v>490</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>10</v>
@@ -8497,18 +8544,18 @@
         <v>18</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="277" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="B277" s="7" t="s">
-        <v>135</v>
+        <v>492</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C277" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>10</v>
@@ -8517,18 +8564,18 @@
         <v>18</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
     </row>
     <row r="278" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="B278" s="7" t="s">
-        <v>135</v>
+        <v>494</v>
+      </c>
+      <c r="B278" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D278" s="4" t="s">
         <v>10</v>
@@ -8537,18 +8584,18 @@
         <v>18</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
     </row>
     <row r="279" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="B279" s="7" t="s">
-        <v>135</v>
+        <v>496</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D279" s="4" t="s">
         <v>10</v>
@@ -8557,18 +8604,18 @@
         <v>18</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="280" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="B280" s="7" t="s">
-        <v>135</v>
+        <v>498</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D280" s="4" t="s">
         <v>10</v>
@@ -8577,18 +8624,18 @@
         <v>18</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="281" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="B281" s="7" t="s">
-        <v>135</v>
+        <v>500</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>10</v>
@@ -8597,18 +8644,18 @@
         <v>18</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="282" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="B282" s="7" t="s">
-        <v>135</v>
+        <v>502</v>
+      </c>
+      <c r="B282" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>10</v>
@@ -8617,18 +8664,18 @@
         <v>18</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
     </row>
     <row r="283" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="B283" s="7" t="s">
-        <v>135</v>
+        <v>504</v>
+      </c>
+      <c r="B283" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C283" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D283" s="4" t="s">
         <v>10</v>
@@ -8637,15 +8684,15 @@
         <v>18</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="284" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="B284" s="7" t="s">
-        <v>135</v>
+        <v>506</v>
+      </c>
+      <c r="B284" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>10</v>
@@ -8657,18 +8704,18 @@
         <v>18</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
     </row>
     <row r="285" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="B285" s="7" t="s">
-        <v>135</v>
+        <v>508</v>
+      </c>
+      <c r="B285" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D285" s="4" t="s">
         <v>10</v>
@@ -8677,15 +8724,15 @@
         <v>18</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
     </row>
     <row r="286" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B286" s="7" t="s">
-        <v>135</v>
+        <v>510</v>
+      </c>
+      <c r="B286" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>10</v>
@@ -8697,18 +8744,18 @@
         <v>18</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
     </row>
     <row r="287" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="B287" s="7" t="s">
-        <v>135</v>
+        <v>512</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>10</v>
@@ -8717,18 +8764,18 @@
         <v>18</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
     </row>
     <row r="288" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="B288" s="7" t="s">
-        <v>135</v>
+        <v>514</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D288" s="4" t="s">
         <v>10</v>
@@ -8737,15 +8784,15 @@
         <v>18</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>508</v>
+        <v>421</v>
       </c>
     </row>
     <row r="289" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="B289" s="7" t="s">
-        <v>135</v>
+        <v>515</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>10</v>
@@ -8757,15 +8804,15 @@
         <v>18</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
     </row>
     <row r="290" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="B290" s="7" t="s">
-        <v>135</v>
+        <v>517</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>10</v>
@@ -8777,18 +8824,18 @@
         <v>18</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
     </row>
     <row r="291" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="B291" s="7" t="s">
-        <v>135</v>
+        <v>519</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>10</v>
@@ -8797,15 +8844,15 @@
         <v>18</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="292" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="B292" s="7" t="s">
-        <v>135</v>
+        <v>521</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>10</v>
@@ -8817,18 +8864,18 @@
         <v>18</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="293" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="B293" s="7" t="s">
-        <v>135</v>
+        <v>523</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>10</v>
@@ -8837,15 +8884,15 @@
         <v>18</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="294" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="B294" s="7" t="s">
-        <v>135</v>
+        <v>525</v>
+      </c>
+      <c r="B294" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>89</v>
@@ -8857,15 +8904,15 @@
         <v>18</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="295" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="B295" s="7" t="s">
-        <v>135</v>
+        <v>527</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>89</v>
@@ -8877,15 +8924,15 @@
         <v>18</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="296" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="B296" s="7" t="s">
-        <v>135</v>
+        <v>529</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C296" s="4" t="s">
         <v>89</v>
@@ -8897,15 +8944,15 @@
         <v>18</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="297" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="B297" s="7" t="s">
-        <v>135</v>
+        <v>531</v>
+      </c>
+      <c r="B297" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C297" s="4" t="s">
         <v>89</v>
@@ -8917,18 +8964,18 @@
         <v>18</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="298" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
-        <v>527</v>
-      </c>
-      <c r="B298" s="7" t="s">
-        <v>135</v>
+        <v>533</v>
+      </c>
+      <c r="B298" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>10</v>
@@ -8937,18 +8984,18 @@
         <v>18</v>
       </c>
       <c r="F298" s="4" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="299" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="B299" s="7" t="s">
-        <v>135</v>
+        <v>535</v>
+      </c>
+      <c r="B299" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>10</v>
@@ -8957,18 +9004,18 @@
         <v>18</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="300" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="B300" s="7" t="s">
-        <v>135</v>
+        <v>537</v>
+      </c>
+      <c r="B300" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>10</v>
@@ -8977,18 +9024,18 @@
         <v>18</v>
       </c>
       <c r="F300" s="4" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="301" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="B301" s="7" t="s">
-        <v>135</v>
+        <v>539</v>
+      </c>
+      <c r="B301" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D301" s="4" t="s">
         <v>10</v>
@@ -8997,18 +9044,18 @@
         <v>18</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="302" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="B302" s="7" t="s">
-        <v>135</v>
+        <v>541</v>
+      </c>
+      <c r="B302" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>10</v>
@@ -9017,15 +9064,15 @@
         <v>18</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="303" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="B303" s="7" t="s">
-        <v>135</v>
+        <v>543</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>89</v>
@@ -9037,18 +9084,18 @@
         <v>18</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="304" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="B304" s="7" t="s">
-        <v>135</v>
+        <v>545</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>10</v>
@@ -9057,35 +9104,35 @@
         <v>18</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="305" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="B305" s="7" t="s">
-        <v>135</v>
+        <v>547</v>
+      </c>
+      <c r="B305" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E305" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F305" s="4" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="306" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
-        <v>543</v>
-      </c>
-      <c r="B306" s="7" t="s">
-        <v>135</v>
+        <v>549</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>10</v>
@@ -9097,18 +9144,18 @@
         <v>18</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="307" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="B307" s="7" t="s">
-        <v>135</v>
+        <v>551</v>
+      </c>
+      <c r="B307" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>10</v>
@@ -9117,18 +9164,18 @@
         <v>18</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="308" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="B308" s="7" t="s">
-        <v>135</v>
+        <v>553</v>
+      </c>
+      <c r="B308" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>10</v>
@@ -9137,15 +9184,15 @@
         <v>18</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="309" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="B309" s="7" t="s">
-        <v>135</v>
+        <v>555</v>
+      </c>
+      <c r="B309" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>10</v>
@@ -9157,15 +9204,15 @@
         <v>18</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="310" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="B310" s="7" t="s">
-        <v>135</v>
+        <v>557</v>
+      </c>
+      <c r="B310" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>10</v>
@@ -9177,15 +9224,15 @@
         <v>18</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
     </row>
     <row r="311" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>553</v>
-      </c>
-      <c r="B311" s="7" t="s">
-        <v>135</v>
+        <v>559</v>
+      </c>
+      <c r="B311" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>10</v>
@@ -9197,18 +9244,18 @@
         <v>18</v>
       </c>
       <c r="F311" s="4" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="312" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="B312" s="7" t="s">
-        <v>135</v>
+        <v>561</v>
+      </c>
+      <c r="B312" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>10</v>
@@ -9217,15 +9264,15 @@
         <v>18</v>
       </c>
       <c r="F312" s="4" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="313" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="B313" s="7" t="s">
-        <v>135</v>
+        <v>563</v>
+      </c>
+      <c r="B313" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>89</v>
@@ -9237,15 +9284,15 @@
         <v>18</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="314" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="B314" s="7" t="s">
-        <v>135</v>
+        <v>565</v>
+      </c>
+      <c r="B314" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>89</v>
@@ -9257,18 +9304,18 @@
         <v>18</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
     </row>
     <row r="315" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="B315" s="7" t="s">
-        <v>135</v>
+        <v>567</v>
+      </c>
+      <c r="B315" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>10</v>
@@ -9277,18 +9324,18 @@
         <v>18</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="316" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="B316" s="7" t="s">
-        <v>135</v>
+        <v>569</v>
+      </c>
+      <c r="B316" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>10</v>
@@ -9297,18 +9344,18 @@
         <v>18</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="317" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="B317" s="7" t="s">
-        <v>135</v>
+        <v>571</v>
+      </c>
+      <c r="B317" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>10</v>
@@ -9317,15 +9364,15 @@
         <v>18</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="318" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="B318" s="7" t="s">
-        <v>135</v>
+        <v>573</v>
+      </c>
+      <c r="B318" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>10</v>
@@ -9337,15 +9384,15 @@
         <v>18</v>
       </c>
       <c r="F318" s="4" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="319" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="B319" s="7" t="s">
-        <v>135</v>
+        <v>575</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C319" s="4" t="s">
         <v>10</v>
@@ -9357,18 +9404,18 @@
         <v>18</v>
       </c>
       <c r="F319" s="4" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="320" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="B320" s="7" t="s">
-        <v>135</v>
+        <v>577</v>
+      </c>
+      <c r="B320" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>10</v>
@@ -9377,15 +9424,15 @@
         <v>18</v>
       </c>
       <c r="F320" s="4" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="321" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="B321" s="7" t="s">
-        <v>135</v>
+        <v>579</v>
+      </c>
+      <c r="B321" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>10</v>
@@ -9397,15 +9444,15 @@
         <v>18</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="322" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="B322" s="7" t="s">
-        <v>135</v>
+        <v>581</v>
+      </c>
+      <c r="B322" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>10</v>
@@ -9417,18 +9464,18 @@
         <v>18</v>
       </c>
       <c r="F322" s="4" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="323" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="B323" s="7" t="s">
-        <v>135</v>
+        <v>583</v>
+      </c>
+      <c r="B323" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>10</v>
@@ -9437,18 +9484,18 @@
         <v>18</v>
       </c>
       <c r="F323" s="4" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="324" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="B324" s="7" t="s">
-        <v>135</v>
+        <v>585</v>
+      </c>
+      <c r="B324" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>10</v>
@@ -9457,15 +9504,15 @@
         <v>18</v>
       </c>
       <c r="F324" s="4" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="325" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="B325" s="7" t="s">
-        <v>135</v>
+        <v>587</v>
+      </c>
+      <c r="B325" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C325" s="4" t="s">
         <v>10</v>
@@ -9477,18 +9524,18 @@
         <v>18</v>
       </c>
       <c r="F325" s="4" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="326" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="B326" s="7" t="s">
-        <v>135</v>
+        <v>589</v>
+      </c>
+      <c r="B326" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>10</v>
@@ -9497,15 +9544,15 @@
         <v>18</v>
       </c>
       <c r="F326" s="4" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="327" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="B327" s="7" t="s">
-        <v>135</v>
+        <v>591</v>
+      </c>
+      <c r="B327" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>10</v>
@@ -9517,15 +9564,15 @@
         <v>18</v>
       </c>
       <c r="F327" s="4" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="328" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="B328" s="7" t="s">
-        <v>135</v>
+        <v>593</v>
+      </c>
+      <c r="B328" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>10</v>
@@ -9537,15 +9584,15 @@
         <v>18</v>
       </c>
       <c r="F328" s="4" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="329" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="B329" s="7" t="s">
-        <v>135</v>
+        <v>595</v>
+      </c>
+      <c r="B329" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>10</v>
@@ -9557,15 +9604,15 @@
         <v>18</v>
       </c>
       <c r="F329" s="4" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="330" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="B330" s="7" t="s">
-        <v>135</v>
+        <v>597</v>
+      </c>
+      <c r="B330" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>10</v>
@@ -9577,18 +9624,18 @@
         <v>18</v>
       </c>
       <c r="F330" s="4" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="331" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="B331" s="7" t="s">
-        <v>135</v>
+        <v>599</v>
+      </c>
+      <c r="B331" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>10</v>
@@ -9597,18 +9644,18 @@
         <v>18</v>
       </c>
       <c r="F331" s="4" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="332" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="B332" s="7" t="s">
-        <v>135</v>
+        <v>601</v>
+      </c>
+      <c r="B332" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>10</v>
@@ -9617,18 +9664,18 @@
         <v>18</v>
       </c>
       <c r="F332" s="4" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="333" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="B333" s="7" t="s">
-        <v>135</v>
+        <v>603</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>10</v>
@@ -9637,15 +9684,15 @@
         <v>18</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="334" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="B334" s="7" t="s">
-        <v>135</v>
+        <v>605</v>
+      </c>
+      <c r="B334" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>10</v>
@@ -9657,15 +9704,15 @@
         <v>18</v>
       </c>
       <c r="F334" s="4" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="335" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="B335" s="7" t="s">
-        <v>135</v>
+        <v>607</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>10</v>
@@ -9677,15 +9724,15 @@
         <v>18</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="336" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="B336" s="7" t="s">
-        <v>135</v>
+        <v>609</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>10</v>
@@ -9697,15 +9744,15 @@
         <v>18</v>
       </c>
       <c r="F336" s="4" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
     </row>
     <row r="337" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="B337" s="7" t="s">
-        <v>135</v>
+        <v>611</v>
+      </c>
+      <c r="B337" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>10</v>
@@ -9717,15 +9764,15 @@
         <v>18</v>
       </c>
       <c r="F337" s="4" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="338" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="B338" s="7" t="s">
-        <v>135</v>
+        <v>613</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>10</v>
@@ -9737,18 +9784,18 @@
         <v>18</v>
       </c>
       <c r="F338" s="4" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="339" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="B339" s="7" t="s">
-        <v>135</v>
+        <v>615</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>10</v>
@@ -9757,15 +9804,15 @@
         <v>18</v>
       </c>
       <c r="F339" s="4" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
     </row>
     <row r="340" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="B340" s="7" t="s">
-        <v>135</v>
+        <v>617</v>
+      </c>
+      <c r="B340" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>10</v>
@@ -9777,15 +9824,15 @@
         <v>18</v>
       </c>
       <c r="F340" s="4" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
     </row>
     <row r="341" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="B341" s="7" t="s">
-        <v>135</v>
+        <v>619</v>
+      </c>
+      <c r="B341" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>10</v>
@@ -9797,15 +9844,15 @@
         <v>18</v>
       </c>
       <c r="F341" s="4" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
     </row>
     <row r="342" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="B342" s="7" t="s">
-        <v>135</v>
+        <v>621</v>
+      </c>
+      <c r="B342" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>10</v>
@@ -9817,15 +9864,15 @@
         <v>18</v>
       </c>
       <c r="F342" s="4" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
     </row>
     <row r="343" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="B343" s="7" t="s">
-        <v>135</v>
+        <v>623</v>
+      </c>
+      <c r="B343" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>10</v>
@@ -9837,15 +9884,15 @@
         <v>18</v>
       </c>
       <c r="F343" s="4" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
     </row>
     <row r="344" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="B344" s="7" t="s">
-        <v>135</v>
+        <v>625</v>
+      </c>
+      <c r="B344" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>10</v>
@@ -9857,18 +9904,18 @@
         <v>18</v>
       </c>
       <c r="F344" s="4" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="345" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="B345" s="7" t="s">
-        <v>135</v>
+        <v>627</v>
+      </c>
+      <c r="B345" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>10</v>
@@ -9877,15 +9924,15 @@
         <v>18</v>
       </c>
       <c r="F345" s="4" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="346" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="B346" s="7" t="s">
-        <v>135</v>
+        <v>629</v>
+      </c>
+      <c r="B346" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C346" s="4" t="s">
         <v>10</v>
@@ -9897,15 +9944,15 @@
         <v>18</v>
       </c>
       <c r="F346" s="4" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
     </row>
     <row r="347" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="B347" s="7" t="s">
-        <v>135</v>
+        <v>631</v>
+      </c>
+      <c r="B347" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>10</v>
@@ -9917,15 +9964,15 @@
         <v>18</v>
       </c>
       <c r="F347" s="4" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
     </row>
     <row r="348" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="B348" s="7" t="s">
-        <v>135</v>
+        <v>633</v>
+      </c>
+      <c r="B348" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>10</v>
@@ -9937,15 +9984,15 @@
         <v>18</v>
       </c>
       <c r="F348" s="4" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
     </row>
     <row r="349" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="B349" s="7" t="s">
-        <v>135</v>
+        <v>635</v>
+      </c>
+      <c r="B349" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>10</v>
@@ -9957,15 +10004,15 @@
         <v>18</v>
       </c>
       <c r="F349" s="4" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
     </row>
     <row r="350" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="B350" s="7" t="s">
-        <v>135</v>
+        <v>637</v>
+      </c>
+      <c r="B350" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C350" s="4" t="s">
         <v>10</v>
@@ -9974,18 +10021,18 @@
         <v>10</v>
       </c>
       <c r="E350" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F350" s="4" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
     </row>
     <row r="351" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="B351" s="7" t="s">
-        <v>135</v>
+        <v>639</v>
+      </c>
+      <c r="B351" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C351" s="4" t="s">
         <v>10</v>
@@ -9997,15 +10044,15 @@
         <v>18</v>
       </c>
       <c r="F351" s="4" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="352" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="B352" s="7" t="s">
-        <v>135</v>
+        <v>641</v>
+      </c>
+      <c r="B352" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C352" s="4" t="s">
         <v>10</v>
@@ -10017,15 +10064,15 @@
         <v>18</v>
       </c>
       <c r="F352" s="4" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
     </row>
     <row r="353" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="B353" s="7" t="s">
-        <v>135</v>
+        <v>643</v>
+      </c>
+      <c r="B353" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C353" s="4" t="s">
         <v>10</v>
@@ -10037,15 +10084,15 @@
         <v>18</v>
       </c>
       <c r="F353" s="4" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
     </row>
     <row r="354" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="B354" s="7" t="s">
-        <v>135</v>
+        <v>645</v>
+      </c>
+      <c r="B354" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C354" s="4" t="s">
         <v>10</v>
@@ -10057,15 +10104,15 @@
         <v>18</v>
       </c>
       <c r="F354" s="4" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="355" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="B355" s="7" t="s">
-        <v>135</v>
+        <v>647</v>
+      </c>
+      <c r="B355" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C355" s="4" t="s">
         <v>10</v>
@@ -10077,15 +10124,15 @@
         <v>18</v>
       </c>
       <c r="F355" s="4" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
     </row>
     <row r="356" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="B356" s="7" t="s">
-        <v>135</v>
+        <v>649</v>
+      </c>
+      <c r="B356" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C356" s="4" t="s">
         <v>10</v>
@@ -10097,15 +10144,15 @@
         <v>18</v>
       </c>
       <c r="F356" s="4" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
     </row>
     <row r="357" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="B357" s="7" t="s">
-        <v>135</v>
+        <v>651</v>
+      </c>
+      <c r="B357" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C357" s="4" t="s">
         <v>10</v>
@@ -10117,15 +10164,15 @@
         <v>18</v>
       </c>
       <c r="F357" s="4" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="358" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="B358" s="7" t="s">
-        <v>135</v>
+        <v>653</v>
+      </c>
+      <c r="B358" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>10</v>
@@ -10137,15 +10184,15 @@
         <v>18</v>
       </c>
       <c r="F358" s="4" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="359" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="B359" s="7" t="s">
-        <v>135</v>
+        <v>655</v>
+      </c>
+      <c r="B359" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C359" s="4" t="s">
         <v>10</v>
@@ -10157,15 +10204,15 @@
         <v>18</v>
       </c>
       <c r="F359" s="4" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
     </row>
     <row r="360" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="B360" s="7" t="s">
-        <v>135</v>
+        <v>657</v>
+      </c>
+      <c r="B360" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C360" s="4" t="s">
         <v>10</v>
@@ -10177,15 +10224,15 @@
         <v>18</v>
       </c>
       <c r="F360" s="4" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="361" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="B361" s="7" t="s">
-        <v>135</v>
+        <v>659</v>
+      </c>
+      <c r="B361" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>10</v>
@@ -10197,15 +10244,15 @@
         <v>18</v>
       </c>
       <c r="F361" s="4" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="362" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A362" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="B362" s="7" t="s">
-        <v>135</v>
+        <v>661</v>
+      </c>
+      <c r="B362" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C362" s="4" t="s">
         <v>10</v>
@@ -10217,15 +10264,15 @@
         <v>18</v>
       </c>
       <c r="F362" s="4" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
     </row>
     <row r="363" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A363" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="B363" s="7" t="s">
-        <v>135</v>
+        <v>663</v>
+      </c>
+      <c r="B363" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>10</v>
@@ -10237,15 +10284,15 @@
         <v>18</v>
       </c>
       <c r="F363" s="4" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
     </row>
     <row r="364" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="B364" s="7" t="s">
-        <v>135</v>
+        <v>665</v>
+      </c>
+      <c r="B364" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C364" s="4" t="s">
         <v>10</v>
@@ -10257,15 +10304,15 @@
         <v>18</v>
       </c>
       <c r="F364" s="4" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="365" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="B365" s="7" t="s">
-        <v>135</v>
+        <v>667</v>
+      </c>
+      <c r="B365" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C365" s="4" t="s">
         <v>10</v>
@@ -10277,15 +10324,15 @@
         <v>18</v>
       </c>
       <c r="F365" s="4" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="366" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A366" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="B366" s="7" t="s">
-        <v>135</v>
+        <v>669</v>
+      </c>
+      <c r="B366" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>10</v>
@@ -10297,15 +10344,15 @@
         <v>18</v>
       </c>
       <c r="F366" s="4" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
     <row r="367" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="B367" s="7" t="s">
-        <v>135</v>
+        <v>671</v>
+      </c>
+      <c r="B367" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>10</v>
@@ -10317,15 +10364,15 @@
         <v>18</v>
       </c>
       <c r="F367" s="4" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
     </row>
     <row r="368" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="B368" s="7" t="s">
-        <v>135</v>
+        <v>673</v>
+      </c>
+      <c r="B368" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C368" s="4" t="s">
         <v>10</v>
@@ -10334,18 +10381,18 @@
         <v>10</v>
       </c>
       <c r="E368" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F368" s="4" t="s">
-        <v>632</v>
+        <v>674</v>
       </c>
     </row>
     <row r="369" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="B369" s="7" t="s">
-        <v>135</v>
+        <v>675</v>
+      </c>
+      <c r="B369" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>10</v>
@@ -10357,15 +10404,15 @@
         <v>18</v>
       </c>
       <c r="F369" s="4" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
     </row>
     <row r="370" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A370" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="B370" s="7" t="s">
-        <v>135</v>
+        <v>677</v>
+      </c>
+      <c r="B370" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>10</v>
@@ -10377,15 +10424,15 @@
         <v>18</v>
       </c>
       <c r="F370" s="4" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
     </row>
     <row r="371" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="B371" s="7" t="s">
-        <v>135</v>
+        <v>679</v>
+      </c>
+      <c r="B371" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>10</v>
@@ -10397,15 +10444,15 @@
         <v>18</v>
       </c>
       <c r="F371" s="4" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
     </row>
     <row r="372" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="B372" s="7" t="s">
-        <v>135</v>
+        <v>681</v>
+      </c>
+      <c r="B372" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C372" s="4" t="s">
         <v>10</v>
@@ -10417,15 +10464,15 @@
         <v>18</v>
       </c>
       <c r="F372" s="4" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
     </row>
     <row r="373" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="B373" s="7" t="s">
-        <v>135</v>
+        <v>683</v>
+      </c>
+      <c r="B373" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C373" s="4" t="s">
         <v>10</v>
@@ -10437,15 +10484,15 @@
         <v>18</v>
       </c>
       <c r="F373" s="4" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
     </row>
     <row r="374" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="B374" s="7" t="s">
-        <v>135</v>
+        <v>685</v>
+      </c>
+      <c r="B374" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C374" s="4" t="s">
         <v>10</v>
@@ -10457,15 +10504,15 @@
         <v>18</v>
       </c>
       <c r="F374" s="4" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
     </row>
     <row r="375" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="B375" s="7" t="s">
-        <v>135</v>
+        <v>687</v>
+      </c>
+      <c r="B375" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>10</v>
@@ -10477,15 +10524,15 @@
         <v>18</v>
       </c>
       <c r="F375" s="4" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
     </row>
     <row r="376" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="B376" s="7" t="s">
-        <v>135</v>
+        <v>689</v>
+      </c>
+      <c r="B376" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>10</v>
@@ -10497,15 +10544,15 @@
         <v>18</v>
       </c>
       <c r="F376" s="4" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
     </row>
     <row r="377" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A377" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="B377" s="7" t="s">
-        <v>135</v>
+        <v>691</v>
+      </c>
+      <c r="B377" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>10</v>
@@ -10517,15 +10564,15 @@
         <v>18</v>
       </c>
       <c r="F377" s="4" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
     </row>
     <row r="378" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="B378" s="7" t="s">
-        <v>135</v>
+        <v>693</v>
+      </c>
+      <c r="B378" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>10</v>
@@ -10537,15 +10584,15 @@
         <v>18</v>
       </c>
       <c r="F378" s="4" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="379" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="4" t="s">
-        <v>688</v>
-      </c>
-      <c r="B379" s="7" t="s">
-        <v>135</v>
+        <v>695</v>
+      </c>
+      <c r="B379" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>10</v>
@@ -10554,18 +10601,18 @@
         <v>10</v>
       </c>
       <c r="E379" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F379" s="4" t="s">
-        <v>632</v>
+        <v>696</v>
       </c>
     </row>
     <row r="380" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A380" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="B380" s="7" t="s">
-        <v>135</v>
+        <v>697</v>
+      </c>
+      <c r="B380" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>10</v>
@@ -10577,15 +10624,15 @@
         <v>18</v>
       </c>
       <c r="F380" s="4" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
     </row>
     <row r="381" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A381" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="B381" s="7" t="s">
-        <v>135</v>
+        <v>699</v>
+      </c>
+      <c r="B381" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C381" s="4" t="s">
         <v>10</v>
@@ -10597,15 +10644,15 @@
         <v>18</v>
       </c>
       <c r="F381" s="4" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="382" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A382" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="B382" s="7" t="s">
-        <v>135</v>
+        <v>701</v>
+      </c>
+      <c r="B382" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C382" s="4" t="s">
         <v>10</v>
@@ -10614,18 +10661,18 @@
         <v>10</v>
       </c>
       <c r="E382" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F382" s="4" t="s">
-        <v>632</v>
+        <v>702</v>
       </c>
     </row>
     <row r="383" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A383" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="B383" s="7" t="s">
-        <v>135</v>
+        <v>703</v>
+      </c>
+      <c r="B383" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C383" s="4" t="s">
         <v>10</v>
@@ -10637,15 +10684,15 @@
         <v>18</v>
       </c>
       <c r="F383" s="4" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
     </row>
     <row r="384" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A384" s="4" t="s">
-        <v>696</v>
-      </c>
-      <c r="B384" s="7" t="s">
-        <v>135</v>
+        <v>705</v>
+      </c>
+      <c r="B384" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C384" s="4" t="s">
         <v>10</v>
@@ -10654,18 +10701,18 @@
         <v>10</v>
       </c>
       <c r="E384" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F384" s="4" t="s">
-        <v>632</v>
+        <v>706</v>
       </c>
     </row>
     <row r="385" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A385" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="B385" s="7" t="s">
-        <v>135</v>
+        <v>707</v>
+      </c>
+      <c r="B385" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C385" s="4" t="s">
         <v>10</v>
@@ -10677,15 +10724,15 @@
         <v>18</v>
       </c>
       <c r="F385" s="4" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
     </row>
     <row r="386" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="4" t="s">
-        <v>699</v>
-      </c>
-      <c r="B386" s="7" t="s">
-        <v>135</v>
+        <v>709</v>
+      </c>
+      <c r="B386" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C386" s="4" t="s">
         <v>10</v>
@@ -10694,18 +10741,18 @@
         <v>10</v>
       </c>
       <c r="E386" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F386" s="4" t="s">
-        <v>632</v>
+        <v>710</v>
       </c>
     </row>
     <row r="387" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="B387" s="7" t="s">
-        <v>135</v>
+        <v>711</v>
+      </c>
+      <c r="B387" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C387" s="4" t="s">
         <v>10</v>
@@ -10717,15 +10764,15 @@
         <v>18</v>
       </c>
       <c r="F387" s="4" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
     </row>
     <row r="388" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="B388" s="7" t="s">
-        <v>135</v>
+        <v>713</v>
+      </c>
+      <c r="B388" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C388" s="4" t="s">
         <v>10</v>
@@ -10737,15 +10784,15 @@
         <v>18</v>
       </c>
       <c r="F388" s="4" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
     </row>
     <row r="389" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="4" t="s">
-        <v>704</v>
-      </c>
-      <c r="B389" s="7" t="s">
-        <v>135</v>
+        <v>715</v>
+      </c>
+      <c r="B389" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>10</v>
@@ -10757,15 +10804,15 @@
         <v>18</v>
       </c>
       <c r="F389" s="4" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
     </row>
     <row r="390" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="B390" s="7" t="s">
-        <v>135</v>
+        <v>717</v>
+      </c>
+      <c r="B390" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>10</v>
@@ -10777,15 +10824,15 @@
         <v>18</v>
       </c>
       <c r="F390" s="4" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
     </row>
     <row r="391" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="B391" s="7" t="s">
-        <v>135</v>
+        <v>719</v>
+      </c>
+      <c r="B391" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C391" s="4" t="s">
         <v>10</v>
@@ -10797,15 +10844,15 @@
         <v>18</v>
       </c>
       <c r="F391" s="4" t="s">
-        <v>618</v>
+        <v>720</v>
       </c>
     </row>
     <row r="392" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="4" t="s">
-        <v>709</v>
-      </c>
-      <c r="B392" s="7" t="s">
-        <v>135</v>
+        <v>721</v>
+      </c>
+      <c r="B392" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C392" s="4" t="s">
         <v>10</v>
@@ -10817,15 +10864,15 @@
         <v>18</v>
       </c>
       <c r="F392" s="4" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
     </row>
     <row r="393" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="B393" s="7" t="s">
-        <v>135</v>
+        <v>723</v>
+      </c>
+      <c r="B393" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>10</v>
@@ -10834,18 +10881,18 @@
         <v>10</v>
       </c>
       <c r="E393" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F393" s="4" t="s">
-        <v>632</v>
+        <v>724</v>
       </c>
     </row>
     <row r="394" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A394" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="B394" s="7" t="s">
-        <v>135</v>
+        <v>725</v>
+      </c>
+      <c r="B394" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C394" s="4" t="s">
         <v>10</v>
@@ -10857,15 +10904,15 @@
         <v>18</v>
       </c>
       <c r="F394" s="4" t="s">
-        <v>713</v>
+        <v>726</v>
       </c>
     </row>
     <row r="395" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A395" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="B395" s="7" t="s">
-        <v>135</v>
+        <v>727</v>
+      </c>
+      <c r="B395" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C395" s="4" t="s">
         <v>10</v>
@@ -10877,15 +10924,15 @@
         <v>18</v>
       </c>
       <c r="F395" s="4" t="s">
-        <v>715</v>
+        <v>728</v>
       </c>
     </row>
     <row r="396" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="B396" s="7" t="s">
-        <v>135</v>
+        <v>729</v>
+      </c>
+      <c r="B396" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C396" s="4" t="s">
         <v>10</v>
@@ -10897,15 +10944,15 @@
         <v>18</v>
       </c>
       <c r="F396" s="4" t="s">
-        <v>717</v>
+        <v>730</v>
       </c>
     </row>
     <row r="397" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A397" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="B397" s="7" t="s">
-        <v>135</v>
+        <v>731</v>
+      </c>
+      <c r="B397" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C397" s="4" t="s">
         <v>10</v>
@@ -10917,15 +10964,15 @@
         <v>18</v>
       </c>
       <c r="F397" s="4" t="s">
-        <v>719</v>
+        <v>732</v>
       </c>
     </row>
     <row r="398" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A398" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="B398" s="7" t="s">
-        <v>135</v>
+        <v>733</v>
+      </c>
+      <c r="B398" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C398" s="4" t="s">
         <v>10</v>
@@ -10937,15 +10984,15 @@
         <v>18</v>
       </c>
       <c r="F398" s="4" t="s">
-        <v>721</v>
+        <v>734</v>
       </c>
     </row>
     <row r="399" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A399" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="B399" s="7" t="s">
-        <v>135</v>
+        <v>735</v>
+      </c>
+      <c r="B399" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C399" s="4" t="s">
         <v>10</v>
@@ -10957,15 +11004,15 @@
         <v>18</v>
       </c>
       <c r="F399" s="4" t="s">
-        <v>504</v>
+        <v>736</v>
       </c>
     </row>
     <row r="400" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A400" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="B400" s="7" t="s">
-        <v>135</v>
+        <v>737</v>
+      </c>
+      <c r="B400" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C400" s="4" t="s">
         <v>10</v>
@@ -10974,18 +11021,18 @@
         <v>10</v>
       </c>
       <c r="E400" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F400" s="4" t="s">
-        <v>632</v>
+        <v>738</v>
       </c>
     </row>
     <row r="401" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="B401" s="7" t="s">
-        <v>135</v>
+        <v>739</v>
+      </c>
+      <c r="B401" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C401" s="4" t="s">
         <v>10</v>
@@ -10997,15 +11044,15 @@
         <v>18</v>
       </c>
       <c r="F401" s="4" t="s">
-        <v>725</v>
+        <v>740</v>
       </c>
     </row>
     <row r="402" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A402" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="B402" s="7" t="s">
-        <v>135</v>
+        <v>741</v>
+      </c>
+      <c r="B402" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C402" s="4" t="s">
         <v>10</v>
@@ -11017,15 +11064,15 @@
         <v>18</v>
       </c>
       <c r="F402" s="4" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
     </row>
     <row r="403" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A403" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="B403" s="7" t="s">
-        <v>135</v>
+        <v>743</v>
+      </c>
+      <c r="B403" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C403" s="4" t="s">
         <v>10</v>
@@ -11037,15 +11084,15 @@
         <v>18</v>
       </c>
       <c r="F403" s="4" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
     </row>
     <row r="404" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A404" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="B404" s="7" t="s">
-        <v>135</v>
+        <v>745</v>
+      </c>
+      <c r="B404" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C404" s="4" t="s">
         <v>10</v>
@@ -11057,15 +11104,15 @@
         <v>18</v>
       </c>
       <c r="F404" s="4" t="s">
-        <v>731</v>
+        <v>662</v>
       </c>
     </row>
     <row r="405" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A405" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="B405" s="7" t="s">
-        <v>135</v>
+        <v>746</v>
+      </c>
+      <c r="B405" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C405" s="4" t="s">
         <v>10</v>
@@ -11077,15 +11124,15 @@
         <v>18</v>
       </c>
       <c r="F405" s="4" t="s">
-        <v>733</v>
+        <v>747</v>
       </c>
     </row>
     <row r="406" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A406" s="4" t="s">
-        <v>734</v>
-      </c>
-      <c r="B406" s="7" t="s">
-        <v>135</v>
+        <v>748</v>
+      </c>
+      <c r="B406" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C406" s="4" t="s">
         <v>10</v>
@@ -11097,15 +11144,15 @@
         <v>18</v>
       </c>
       <c r="F406" s="4" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
     </row>
     <row r="407" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="B407" s="7" t="s">
-        <v>135</v>
+        <v>750</v>
+      </c>
+      <c r="B407" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>10</v>
@@ -11117,15 +11164,15 @@
         <v>18</v>
       </c>
       <c r="F407" s="4" t="s">
-        <v>504</v>
+        <v>751</v>
       </c>
     </row>
     <row r="408" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="B408" s="7" t="s">
-        <v>135</v>
+        <v>752</v>
+      </c>
+      <c r="B408" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C408" s="4" t="s">
         <v>10</v>
@@ -11137,15 +11184,15 @@
         <v>18</v>
       </c>
       <c r="F408" s="4" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
     </row>
     <row r="409" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="B409" s="7" t="s">
-        <v>135</v>
+        <v>754</v>
+      </c>
+      <c r="B409" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C409" s="4" t="s">
         <v>10</v>
@@ -11157,15 +11204,15 @@
         <v>18</v>
       </c>
       <c r="F409" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="410" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A410" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="B410" s="7" t="s">
-        <v>135</v>
+        <v>756</v>
+      </c>
+      <c r="B410" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C410" s="4" t="s">
         <v>10</v>
@@ -11174,18 +11221,18 @@
         <v>10</v>
       </c>
       <c r="E410" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F410" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
     </row>
     <row r="411" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="4" t="s">
-        <v>743</v>
-      </c>
-      <c r="B411" s="7" t="s">
-        <v>135</v>
+        <v>758</v>
+      </c>
+      <c r="B411" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C411" s="4" t="s">
         <v>10</v>
@@ -11197,15 +11244,15 @@
         <v>18</v>
       </c>
       <c r="F411" s="4" t="s">
-        <v>744</v>
+        <v>550</v>
       </c>
     </row>
     <row r="412" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A412" s="4" t="s">
-        <v>745</v>
-      </c>
-      <c r="B412" s="7" t="s">
-        <v>135</v>
+        <v>759</v>
+      </c>
+      <c r="B412" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C412" s="4" t="s">
         <v>10</v>
@@ -11214,21 +11261,21 @@
         <v>10</v>
       </c>
       <c r="E412" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F412" s="4" t="s">
-        <v>746</v>
+        <v>760</v>
       </c>
     </row>
     <row r="413" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A413" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="B413" s="7" t="s">
-        <v>135</v>
+        <v>761</v>
+      </c>
+      <c r="B413" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>10</v>
@@ -11237,15 +11284,15 @@
         <v>18</v>
       </c>
       <c r="F413" s="4" t="s">
-        <v>748</v>
+        <v>762</v>
       </c>
     </row>
     <row r="414" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A414" s="4" t="s">
-        <v>749</v>
-      </c>
-      <c r="B414" s="7" t="s">
-        <v>135</v>
+        <v>763</v>
+      </c>
+      <c r="B414" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C414" s="4" t="s">
         <v>10</v>
@@ -11257,15 +11304,15 @@
         <v>18</v>
       </c>
       <c r="F414" s="4" t="s">
-        <v>750</v>
+        <v>764</v>
       </c>
     </row>
     <row r="415" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A415" s="4" t="s">
-        <v>751</v>
-      </c>
-      <c r="B415" s="7" t="s">
-        <v>135</v>
+        <v>765</v>
+      </c>
+      <c r="B415" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C415" s="4" t="s">
         <v>10</v>
@@ -11277,15 +11324,15 @@
         <v>18</v>
       </c>
       <c r="F415" s="4" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
     </row>
     <row r="416" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="B416" s="7" t="s">
-        <v>135</v>
+        <v>767</v>
+      </c>
+      <c r="B416" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C416" s="4" t="s">
         <v>10</v>
@@ -11297,15 +11344,15 @@
         <v>18</v>
       </c>
       <c r="F416" s="4" t="s">
-        <v>754</v>
+        <v>768</v>
       </c>
     </row>
     <row r="417" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A417" s="4" t="s">
-        <v>755</v>
-      </c>
-      <c r="B417" s="7" t="s">
-        <v>135</v>
+        <v>769</v>
+      </c>
+      <c r="B417" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C417" s="4" t="s">
         <v>10</v>
@@ -11317,15 +11364,15 @@
         <v>18</v>
       </c>
       <c r="F417" s="4" t="s">
-        <v>756</v>
+        <v>770</v>
       </c>
     </row>
     <row r="418" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A418" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="B418" s="7" t="s">
-        <v>135</v>
+        <v>771</v>
+      </c>
+      <c r="B418" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C418" s="4" t="s">
         <v>10</v>
@@ -11334,18 +11381,18 @@
         <v>10</v>
       </c>
       <c r="E418" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F418" s="4" t="s">
-        <v>758</v>
+        <v>550</v>
       </c>
     </row>
     <row r="419" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A419" s="4" t="s">
-        <v>759</v>
-      </c>
-      <c r="B419" s="7" t="s">
-        <v>135</v>
+        <v>772</v>
+      </c>
+      <c r="B419" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C419" s="4" t="s">
         <v>10</v>
@@ -11354,18 +11401,18 @@
         <v>10</v>
       </c>
       <c r="E419" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F419" s="4" t="s">
-        <v>760</v>
+        <v>773</v>
       </c>
     </row>
     <row r="420" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A420" s="4" t="s">
-        <v>761</v>
-      </c>
-      <c r="B420" s="7" t="s">
-        <v>135</v>
+        <v>774</v>
+      </c>
+      <c r="B420" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C420" s="4" t="s">
         <v>10</v>
@@ -11377,15 +11424,15 @@
         <v>18</v>
       </c>
       <c r="F420" s="4" t="s">
-        <v>762</v>
+        <v>775</v>
       </c>
     </row>
     <row r="421" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A421" s="4" t="s">
-        <v>763</v>
-      </c>
-      <c r="B421" s="7" t="s">
-        <v>135</v>
+        <v>776</v>
+      </c>
+      <c r="B421" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C421" s="4" t="s">
         <v>10</v>
@@ -11397,18 +11444,18 @@
         <v>18</v>
       </c>
       <c r="F421" s="4" t="s">
-        <v>764</v>
+        <v>777</v>
       </c>
     </row>
     <row r="422" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A422" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="B422" s="7" t="s">
-        <v>135</v>
+        <v>778</v>
+      </c>
+      <c r="B422" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>10</v>
@@ -11417,15 +11464,15 @@
         <v>18</v>
       </c>
       <c r="F422" s="4" t="s">
-        <v>766</v>
+        <v>779</v>
       </c>
     </row>
     <row r="423" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A423" s="4" t="s">
-        <v>767</v>
-      </c>
-      <c r="B423" s="7" t="s">
-        <v>135</v>
+        <v>780</v>
+      </c>
+      <c r="B423" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>10</v>
@@ -11437,15 +11484,15 @@
         <v>18</v>
       </c>
       <c r="F423" s="4" t="s">
-        <v>768</v>
+        <v>781</v>
       </c>
     </row>
     <row r="424" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="B424" s="7" t="s">
-        <v>135</v>
+        <v>782</v>
+      </c>
+      <c r="B424" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C424" s="4" t="s">
         <v>10</v>
@@ -11457,15 +11504,15 @@
         <v>18</v>
       </c>
       <c r="F424" s="4" t="s">
-        <v>770</v>
+        <v>783</v>
       </c>
     </row>
     <row r="425" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="B425" s="7" t="s">
-        <v>135</v>
+        <v>784</v>
+      </c>
+      <c r="B425" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C425" s="4" t="s">
         <v>10</v>
@@ -11474,18 +11521,18 @@
         <v>10</v>
       </c>
       <c r="E425" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F425" s="4" t="s">
-        <v>772</v>
+        <v>785</v>
       </c>
     </row>
     <row r="426" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="4" t="s">
-        <v>773</v>
-      </c>
-      <c r="B426" s="7" t="s">
-        <v>135</v>
+        <v>786</v>
+      </c>
+      <c r="B426" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C426" s="4" t="s">
         <v>10</v>
@@ -11494,18 +11541,18 @@
         <v>10</v>
       </c>
       <c r="E426" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F426" s="4" t="s">
-        <v>774</v>
+        <v>787</v>
       </c>
     </row>
     <row r="427" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A427" s="4" t="s">
-        <v>775</v>
-      </c>
-      <c r="B427" s="7" t="s">
-        <v>135</v>
+        <v>788</v>
+      </c>
+      <c r="B427" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C427" s="4" t="s">
         <v>10</v>
@@ -11514,18 +11561,18 @@
         <v>10</v>
       </c>
       <c r="E427" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F427" s="4" t="s">
-        <v>776</v>
+        <v>789</v>
       </c>
     </row>
     <row r="428" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="4" t="s">
-        <v>777</v>
-      </c>
-      <c r="B428" s="7" t="s">
-        <v>135</v>
+        <v>790</v>
+      </c>
+      <c r="B428" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C428" s="4" t="s">
         <v>10</v>
@@ -11534,18 +11581,18 @@
         <v>10</v>
       </c>
       <c r="E428" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F428" s="4" t="s">
-        <v>778</v>
+        <v>791</v>
       </c>
     </row>
     <row r="429" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A429" s="4" t="s">
-        <v>779</v>
-      </c>
-      <c r="B429" s="7" t="s">
-        <v>135</v>
+        <v>792</v>
+      </c>
+      <c r="B429" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C429" s="4" t="s">
         <v>10</v>
@@ -11557,15 +11604,15 @@
         <v>18</v>
       </c>
       <c r="F429" s="4" t="s">
-        <v>780</v>
+        <v>793</v>
       </c>
     </row>
     <row r="430" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="4" t="s">
-        <v>781</v>
-      </c>
-      <c r="B430" s="7" t="s">
-        <v>135</v>
+        <v>794</v>
+      </c>
+      <c r="B430" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C430" s="4" t="s">
         <v>10</v>
@@ -11577,15 +11624,15 @@
         <v>18</v>
       </c>
       <c r="F430" s="4" t="s">
-        <v>782</v>
+        <v>795</v>
       </c>
     </row>
     <row r="431" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="4" t="s">
-        <v>783</v>
-      </c>
-      <c r="B431" s="7" t="s">
-        <v>135</v>
+        <v>796</v>
+      </c>
+      <c r="B431" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C431" s="4" t="s">
         <v>10</v>
@@ -11597,15 +11644,15 @@
         <v>18</v>
       </c>
       <c r="F431" s="4" t="s">
-        <v>784</v>
+        <v>797</v>
       </c>
     </row>
     <row r="432" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="4" t="s">
-        <v>785</v>
-      </c>
-      <c r="B432" s="7" t="s">
-        <v>135</v>
+        <v>798</v>
+      </c>
+      <c r="B432" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C432" s="4" t="s">
         <v>10</v>
@@ -11617,15 +11664,15 @@
         <v>18</v>
       </c>
       <c r="F432" s="4" t="s">
-        <v>786</v>
+        <v>799</v>
       </c>
     </row>
     <row r="433" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="4" t="s">
-        <v>787</v>
-      </c>
-      <c r="B433" s="7" t="s">
-        <v>135</v>
+        <v>800</v>
+      </c>
+      <c r="B433" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C433" s="4" t="s">
         <v>10</v>
@@ -11637,15 +11684,15 @@
         <v>18</v>
       </c>
       <c r="F433" s="4" t="s">
-        <v>788</v>
+        <v>801</v>
       </c>
     </row>
     <row r="434" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A434" s="4" t="s">
-        <v>789</v>
-      </c>
-      <c r="B434" s="7" t="s">
-        <v>135</v>
+        <v>802</v>
+      </c>
+      <c r="B434" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C434" s="4" t="s">
         <v>10</v>
@@ -11657,15 +11704,15 @@
         <v>18</v>
       </c>
       <c r="F434" s="4" t="s">
-        <v>790</v>
+        <v>803</v>
       </c>
     </row>
     <row r="435" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A435" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="B435" s="7" t="s">
-        <v>135</v>
+        <v>804</v>
+      </c>
+      <c r="B435" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C435" s="4" t="s">
         <v>10</v>
@@ -11677,15 +11724,15 @@
         <v>18</v>
       </c>
       <c r="F435" s="4" t="s">
-        <v>792</v>
+        <v>805</v>
       </c>
     </row>
     <row r="436" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A436" s="4" t="s">
-        <v>793</v>
-      </c>
-      <c r="B436" s="7" t="s">
-        <v>135</v>
+        <v>806</v>
+      </c>
+      <c r="B436" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C436" s="4" t="s">
         <v>10</v>
@@ -11697,18 +11744,18 @@
         <v>18</v>
       </c>
       <c r="F436" s="4" t="s">
-        <v>794</v>
+        <v>807</v>
       </c>
     </row>
     <row r="437" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A437" s="4" t="s">
-        <v>795</v>
-      </c>
-      <c r="B437" s="7" t="s">
-        <v>135</v>
+        <v>808</v>
+      </c>
+      <c r="B437" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>10</v>
@@ -11717,15 +11764,15 @@
         <v>18</v>
       </c>
       <c r="F437" s="4" t="s">
-        <v>796</v>
+        <v>809</v>
       </c>
     </row>
     <row r="438" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A438" s="4" t="s">
-        <v>797</v>
-      </c>
-      <c r="B438" s="7" t="s">
-        <v>135</v>
+        <v>810</v>
+      </c>
+      <c r="B438" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C438" s="4" t="s">
         <v>10</v>
@@ -11737,18 +11784,18 @@
         <v>18</v>
       </c>
       <c r="F438" s="4" t="s">
-        <v>798</v>
+        <v>811</v>
       </c>
     </row>
     <row r="439" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A439" s="4" t="s">
-        <v>799</v>
-      </c>
-      <c r="B439" s="7" t="s">
-        <v>135</v>
+        <v>812</v>
+      </c>
+      <c r="B439" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>10</v>
@@ -11757,15 +11804,15 @@
         <v>18</v>
       </c>
       <c r="F439" s="4" t="s">
-        <v>800</v>
+        <v>813</v>
       </c>
     </row>
     <row r="440" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A440" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="B440" s="7" t="s">
-        <v>135</v>
+        <v>814</v>
+      </c>
+      <c r="B440" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>10</v>
@@ -11777,15 +11824,15 @@
         <v>18</v>
       </c>
       <c r="F440" s="4" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="441" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A441" s="4" t="s">
-        <v>803</v>
-      </c>
-      <c r="B441" s="7" t="s">
-        <v>135</v>
+        <v>816</v>
+      </c>
+      <c r="B441" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C441" s="4" t="s">
         <v>10</v>
@@ -11797,15 +11844,15 @@
         <v>18</v>
       </c>
       <c r="F441" s="4" t="s">
-        <v>804</v>
+        <v>817</v>
       </c>
     </row>
     <row r="442" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A442" s="4" t="s">
-        <v>805</v>
-      </c>
-      <c r="B442" s="7" t="s">
-        <v>135</v>
+        <v>818</v>
+      </c>
+      <c r="B442" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C442" s="4" t="s">
         <v>10</v>
@@ -11817,15 +11864,15 @@
         <v>18</v>
       </c>
       <c r="F442" s="4" t="s">
-        <v>806</v>
+        <v>819</v>
       </c>
     </row>
     <row r="443" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A443" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="B443" s="7" t="s">
-        <v>135</v>
+        <v>820</v>
+      </c>
+      <c r="B443" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C443" s="4" t="s">
         <v>10</v>
@@ -11837,15 +11884,15 @@
         <v>18</v>
       </c>
       <c r="F443" s="4" t="s">
-        <v>808</v>
+        <v>821</v>
       </c>
     </row>
     <row r="444" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A444" s="4" t="s">
-        <v>809</v>
-      </c>
-      <c r="B444" s="7" t="s">
-        <v>135</v>
+        <v>822</v>
+      </c>
+      <c r="B444" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C444" s="4" t="s">
         <v>10</v>
@@ -11857,15 +11904,15 @@
         <v>18</v>
       </c>
       <c r="F444" s="4" t="s">
-        <v>810</v>
+        <v>823</v>
       </c>
     </row>
     <row r="445" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A445" s="4" t="s">
-        <v>811</v>
-      </c>
-      <c r="B445" s="7" t="s">
-        <v>135</v>
+        <v>824</v>
+      </c>
+      <c r="B445" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C445" s="4" t="s">
         <v>10</v>
@@ -11877,15 +11924,15 @@
         <v>18</v>
       </c>
       <c r="F445" s="4" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
     </row>
     <row r="446" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A446" s="4" t="s">
-        <v>813</v>
-      </c>
-      <c r="B446" s="7" t="s">
-        <v>135</v>
+        <v>826</v>
+      </c>
+      <c r="B446" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C446" s="4" t="s">
         <v>10</v>
@@ -11897,15 +11944,15 @@
         <v>18</v>
       </c>
       <c r="F446" s="4" t="s">
-        <v>814</v>
+        <v>827</v>
       </c>
     </row>
     <row r="447" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A447" s="4" t="s">
-        <v>815</v>
-      </c>
-      <c r="B447" s="7" t="s">
-        <v>135</v>
+        <v>828</v>
+      </c>
+      <c r="B447" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C447" s="4" t="s">
         <v>10</v>
@@ -11914,38 +11961,38 @@
         <v>10</v>
       </c>
       <c r="E447" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F447" s="4" t="s">
-        <v>816</v>
+        <v>829</v>
       </c>
     </row>
     <row r="448" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A448" s="4" t="s">
-        <v>817</v>
-      </c>
-      <c r="B448" s="7" t="s">
-        <v>135</v>
+        <v>830</v>
+      </c>
+      <c r="B448" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D448" s="4" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E448" s="4" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F448" s="4" t="s">
-        <v>818</v>
+        <v>831</v>
       </c>
     </row>
     <row r="449" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A449" s="4" t="s">
-        <v>819</v>
-      </c>
-      <c r="B449" s="7" t="s">
-        <v>135</v>
+        <v>832</v>
+      </c>
+      <c r="B449" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C449" s="4" t="s">
         <v>89</v>
@@ -11957,15 +12004,15 @@
         <v>18</v>
       </c>
       <c r="F449" s="4" t="s">
-        <v>554</v>
+        <v>598</v>
       </c>
     </row>
     <row r="450" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="B450" s="7" t="s">
-        <v>135</v>
+        <v>833</v>
+      </c>
+      <c r="B450" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C450" s="4" t="s">
         <v>89</v>
@@ -11977,15 +12024,15 @@
         <v>18</v>
       </c>
       <c r="F450" s="4" t="s">
-        <v>821</v>
+        <v>834</v>
       </c>
     </row>
     <row r="451" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="4" t="s">
-        <v>822</v>
-      </c>
-      <c r="B451" s="7" t="s">
-        <v>135</v>
+        <v>835</v>
+      </c>
+      <c r="B451" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>89</v>
@@ -11997,15 +12044,15 @@
         <v>18</v>
       </c>
       <c r="F451" s="4" t="s">
-        <v>823</v>
+        <v>836</v>
       </c>
     </row>
     <row r="452" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="4" t="s">
-        <v>824</v>
-      </c>
-      <c r="B452" s="7" t="s">
-        <v>135</v>
+        <v>837</v>
+      </c>
+      <c r="B452" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>89</v>
@@ -12017,15 +12064,15 @@
         <v>18</v>
       </c>
       <c r="F452" s="4" t="s">
-        <v>825</v>
+        <v>838</v>
       </c>
     </row>
     <row r="453" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="B453" s="7" t="s">
-        <v>135</v>
+        <v>839</v>
+      </c>
+      <c r="B453" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C453" s="4" t="s">
         <v>89</v>
@@ -12037,15 +12084,15 @@
         <v>18</v>
       </c>
       <c r="F453" s="4" t="s">
-        <v>827</v>
+        <v>840</v>
       </c>
     </row>
     <row r="454" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="4" t="s">
-        <v>828</v>
-      </c>
-      <c r="B454" s="7" t="s">
-        <v>135</v>
+        <v>841</v>
+      </c>
+      <c r="B454" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C454" s="4" t="s">
         <v>89</v>
@@ -12057,15 +12104,15 @@
         <v>18</v>
       </c>
       <c r="F454" s="4" t="s">
-        <v>829</v>
+        <v>842</v>
       </c>
     </row>
     <row r="455" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="4" t="s">
-        <v>830</v>
-      </c>
-      <c r="B455" s="7" t="s">
-        <v>135</v>
+        <v>843</v>
+      </c>
+      <c r="B455" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C455" s="4" t="s">
         <v>89</v>
@@ -12077,15 +12124,15 @@
         <v>18</v>
       </c>
       <c r="F455" s="4" t="s">
-        <v>831</v>
+        <v>844</v>
       </c>
     </row>
     <row r="456" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="4" t="s">
-        <v>832</v>
-      </c>
-      <c r="B456" s="7" t="s">
-        <v>135</v>
+        <v>845</v>
+      </c>
+      <c r="B456" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C456" s="4" t="s">
         <v>89</v>
@@ -12097,15 +12144,15 @@
         <v>18</v>
       </c>
       <c r="F456" s="4" t="s">
-        <v>833</v>
+        <v>846</v>
       </c>
     </row>
     <row r="457" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="4" t="s">
-        <v>834</v>
-      </c>
-      <c r="B457" s="7" t="s">
-        <v>135</v>
+        <v>847</v>
+      </c>
+      <c r="B457" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C457" s="4" t="s">
         <v>89</v>
@@ -12117,15 +12164,15 @@
         <v>18</v>
       </c>
       <c r="F457" s="4" t="s">
-        <v>835</v>
+        <v>848</v>
       </c>
     </row>
     <row r="458" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="4" t="s">
-        <v>836</v>
-      </c>
-      <c r="B458" s="7" t="s">
-        <v>135</v>
+        <v>849</v>
+      </c>
+      <c r="B458" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>89</v>
@@ -12137,15 +12184,15 @@
         <v>18</v>
       </c>
       <c r="F458" s="4" t="s">
-        <v>837</v>
+        <v>850</v>
       </c>
     </row>
     <row r="459" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A459" s="4" t="s">
-        <v>838</v>
-      </c>
-      <c r="B459" s="7" t="s">
-        <v>135</v>
+        <v>851</v>
+      </c>
+      <c r="B459" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="C459" s="4" t="s">
         <v>89</v>
@@ -12157,7 +12204,7 @@
         <v>18</v>
       </c>
       <c r="F459" s="4" t="s">
-        <v>839</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -12172,7 +12219,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -12181,21 +12228,21 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>840</v>
+        <v>853</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>841</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>842</v>
+      <c r="A2" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>855</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>843</v>
+        <v>856</v>
       </c>
       <c r="B3">
         <v>456</v>
@@ -12222,31 +12269,39 @@
         <v>135</v>
       </c>
       <c r="B6">
-        <v>370</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>844</v>
+        <v>306</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="B8">
-        <v>1369</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="B9">
-        <v>6961</v>
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>859</v>
+      </c>
+      <c r="B10">
+        <v>6963</v>
       </c>
     </row>
   </sheetData>
